--- a/input_data/admin_data/COL/_clean/total-pre-COL-adults.xlsx
+++ b/input_data/admin_data/COL/_clean/total-pre-COL-adults.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1847" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="2160" uniqueCount="11">
   <si>
     <t>poptot</t>
   </si>
@@ -139,22 +139,22 @@
         <v>30643644</v>
       </c>
       <c r="B2" s="2">
-        <v>12232738.022099448</v>
+        <v>10686888.964735517</v>
       </c>
       <c r="C2" s="2">
-        <v>109677962592256</v>
+        <v>67484384231424</v>
       </c>
       <c r="D2" s="1">
-        <v>0.95003575086593628</v>
+        <v>0.95002275705337524</v>
       </c>
       <c r="E2" s="2">
-        <v>28407587.816538274</v>
+        <v>25127043.852584064</v>
       </c>
       <c r="F2" s="1">
-        <v>5494283</v>
+        <v>3384690.25</v>
       </c>
       <c r="G2" s="1">
-        <v>0.0022275620140135288</v>
+        <v>0.0027409023605287075</v>
       </c>
       <c r="H2" s="1">
         <v>2014</v>
@@ -168,22 +168,22 @@
         <v>30643644</v>
       </c>
       <c r="B3" s="2">
-        <v>39628476.468368478</v>
+        <v>33651260.570725709</v>
       </c>
       <c r="C3" s="2">
-        <v>129953907605504</v>
+        <v>78088083865600</v>
       </c>
       <c r="D3" s="1">
-        <v>0.96001219749450684</v>
+        <v>0.96002906560897827</v>
       </c>
       <c r="E3" s="2">
-        <v>47311355.924266398</v>
+        <v>38615274.213988274</v>
       </c>
       <c r="F3" s="1">
-        <v>5494283</v>
+        <v>3384690.25</v>
       </c>
       <c r="G3" s="1">
-        <v>0.0048309573903679848</v>
+        <v>0.0059095057658851147</v>
       </c>
       <c r="H3" s="1"/>
       <c r="I3" t="s">
@@ -195,22 +195,22 @@
         <v>30643644</v>
       </c>
       <c r="B4" s="2">
-        <v>56178060.092250921</v>
+        <v>43759192.745657556</v>
       </c>
       <c r="C4" s="2">
-        <v>157664004800512</v>
+        <v>91257158238208</v>
       </c>
       <c r="D4" s="1">
-        <v>0.97005331516265869</v>
+        <v>0.9700283408164978</v>
       </c>
       <c r="E4" s="2">
-        <v>68080227.879633173</v>
+        <v>49589549.220520459</v>
       </c>
       <c r="F4" s="1">
-        <v>5494283</v>
+        <v>3384690.25</v>
       </c>
       <c r="G4" s="1">
-        <v>0.010106450878083706</v>
+        <v>0.014039983041584492</v>
       </c>
       <c r="H4" s="1"/>
       <c r="I4" t="s">
@@ -222,22 +222,22 @@
         <v>30643644</v>
       </c>
       <c r="B5" s="2">
-        <v>82491287.299630076</v>
+        <v>56011850.432632886</v>
       </c>
       <c r="C5" s="2">
-        <v>202455514087424</v>
+        <v>112185216860160</v>
       </c>
       <c r="D5" s="1">
-        <v>0.98003548383712769</v>
+        <v>0.98004895448684692</v>
       </c>
       <c r="E5" s="2">
-        <v>103337434.99847336</v>
+        <v>66065042.205339752</v>
       </c>
       <c r="F5" s="1">
-        <v>5494283</v>
+        <v>3384690.25</v>
       </c>
       <c r="G5" s="1">
-        <v>0.017856409773230553</v>
+        <v>0.028088059276342392</v>
       </c>
       <c r="H5" s="1"/>
       <c r="I5" t="s">
@@ -249,22 +249,22 @@
         <v>30643644</v>
       </c>
       <c r="B6" s="2">
-        <v>133312861.31611316</v>
+        <v>87428372.164316371</v>
       </c>
       <c r="C6" s="2">
-        <v>301574584795136</v>
+        <v>158232735645696</v>
       </c>
       <c r="D6" s="1">
-        <v>0.99001777172088623</v>
+        <v>0.9900166392326355</v>
       </c>
       <c r="E6" s="2">
-        <v>137822825.06270424</v>
+        <v>89774181.73586978</v>
       </c>
       <c r="F6" s="1">
-        <v>5494283</v>
+        <v>3384690.25</v>
       </c>
       <c r="G6" s="1">
-        <v>0.032092999666929245</v>
+        <v>0.048362426459789276</v>
       </c>
       <c r="H6" s="1"/>
       <c r="I6" t="s">
@@ -276,22 +276,22 @@
         <v>30643644</v>
       </c>
       <c r="B7" s="2">
-        <v>143064433.29253367</v>
+        <v>92813638.15384616</v>
       </c>
       <c r="C7" s="2">
-        <v>319979559845888</v>
+        <v>165941396635648</v>
       </c>
       <c r="D7" s="1">
-        <v>0.99102640151977539</v>
+        <v>0.99102699756622314</v>
       </c>
       <c r="E7" s="2">
-        <v>148212195.93583438</v>
+        <v>96569026.979671106</v>
       </c>
       <c r="F7" s="1">
-        <v>5494283</v>
+        <v>3384690.25</v>
       </c>
       <c r="G7" s="1">
-        <v>0.0354728102684021</v>
+        <v>0.054191432893276215</v>
       </c>
       <c r="H7" s="1"/>
       <c r="I7" t="s">
@@ -303,22 +303,22 @@
         <v>30643644</v>
       </c>
       <c r="B8" s="2">
-        <v>154363973.27641279</v>
+        <v>99413890.318627447</v>
       </c>
       <c r="C8" s="2">
-        <v>341740447858688</v>
+        <v>174721769406464</v>
       </c>
       <c r="D8" s="1">
-        <v>0.9920353889465332</v>
+        <v>0.99203509092330933</v>
       </c>
       <c r="E8" s="2">
-        <v>160658054.1723814</v>
+        <v>102235921.54617473</v>
       </c>
       <c r="F8" s="1">
-        <v>5494283</v>
+        <v>3384690.25</v>
       </c>
       <c r="G8" s="1">
-        <v>0.037771545350551605</v>
+        <v>0.05893336609005928</v>
       </c>
       <c r="H8" s="1"/>
       <c r="I8" t="s">
@@ -330,22 +330,22 @@
         <v>30643644</v>
       </c>
       <c r="B9" s="2">
-        <v>168219078.57581341</v>
+        <v>105724635.83282113</v>
       </c>
       <c r="C9" s="2">
-        <v>368003535339520</v>
+        <v>185238919577600</v>
       </c>
       <c r="D9" s="1">
-        <v>0.99304425716400146</v>
+        <v>0.99304431676864624</v>
       </c>
       <c r="E9" s="2">
-        <v>176149690.08700711</v>
+        <v>109448385.83582041</v>
       </c>
       <c r="F9" s="1">
-        <v>5494283</v>
+        <v>3384690.25</v>
       </c>
       <c r="G9" s="1">
-        <v>0.039839901030063629</v>
+        <v>0.063126973807811737</v>
       </c>
       <c r="H9" s="1"/>
       <c r="I9" t="s">
@@ -357,22 +357,22 @@
         <v>30643644</v>
       </c>
       <c r="B10" s="2">
-        <v>185444208.973571</v>
+        <v>113204361.40135218</v>
       </c>
       <c r="C10" s="2">
-        <v>400552777220096</v>
+        <v>197310613028864</v>
       </c>
       <c r="D10" s="1">
-        <v>0.99405312538146973</v>
+        <v>0.99400001764297485</v>
       </c>
       <c r="E10" s="2">
-        <v>194792938.32177001</v>
+        <v>117600686.5939582</v>
       </c>
       <c r="F10" s="1">
-        <v>5494283</v>
+        <v>3384690.25</v>
       </c>
       <c r="G10" s="1">
-        <v>0.041206996887922287</v>
+        <v>0.068217568099498749</v>
       </c>
       <c r="H10" s="1"/>
       <c r="I10" t="s">
@@ -384,22 +384,22 @@
         <v>30643644</v>
       </c>
       <c r="B11" s="2">
-        <v>206066562.31857318</v>
+        <v>123282839.16513199</v>
       </c>
       <c r="C11" s="2">
-        <v>439954505203712</v>
+        <v>213424155918336</v>
       </c>
       <c r="D11" s="1">
         <v>0.99500894546508789</v>
       </c>
       <c r="E11" s="2">
-        <v>219165640.07375294</v>
+        <v>129836115.90712346</v>
       </c>
       <c r="F11" s="1">
-        <v>5494283</v>
+        <v>3384690.25</v>
       </c>
       <c r="G11" s="1">
-        <v>0.044064141809940338</v>
+        <v>0.074860766530036926</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" t="s">
@@ -411,22 +411,22 @@
         <v>30643644</v>
       </c>
       <c r="B12" s="2">
-        <v>235586355.86969882</v>
+        <v>137062964.35156733</v>
       </c>
       <c r="C12" s="2">
-        <v>495886723448832</v>
+        <v>234597908480000</v>
       </c>
       <c r="D12" s="1">
-        <v>0.99601775407791138</v>
+        <v>0.9960176944732666</v>
       </c>
       <c r="E12" s="2">
-        <v>254652931.80740744</v>
+        <v>144799837.54321388</v>
       </c>
       <c r="F12" s="1">
-        <v>5494283</v>
+        <v>3384690.25</v>
       </c>
       <c r="G12" s="1">
-        <v>0.047493357211351395</v>
+        <v>0.083002790808677673</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" t="s">
@@ -438,22 +438,22 @@
         <v>30643644</v>
       </c>
       <c r="B13" s="2">
-        <v>278401554.00614625</v>
+        <v>156319580.82360175</v>
       </c>
       <c r="C13" s="2">
-        <v>577735646773248</v>
+        <v>265066725244928</v>
       </c>
       <c r="D13" s="1">
         <v>0.99702662229537964</v>
       </c>
       <c r="E13" s="2">
-        <v>307507313.33260012</v>
+        <v>165463967.48592964</v>
       </c>
       <c r="F13" s="1">
-        <v>5494283</v>
+        <v>3384690.25</v>
       </c>
       <c r="G13" s="1">
-        <v>0.049107853323221207</v>
+        <v>0.091954521834850311</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" t="s">
@@ -465,22 +465,22 @@
         <v>30643644</v>
       </c>
       <c r="B14" s="2">
-        <v>347909494.16103256</v>
+        <v>178808581.18081182</v>
       </c>
       <c r="C14" s="2">
-        <v>716499060785152</v>
+        <v>316218175127552</v>
       </c>
       <c r="D14" s="1">
-        <v>0.99803543090820313</v>
+        <v>0.9980354905128479</v>
       </c>
       <c r="E14" s="2">
-        <v>408178109.54937738</v>
+        <v>193774365.86251736</v>
       </c>
       <c r="F14" s="1">
-        <v>5494283</v>
+        <v>3384690.25</v>
       </c>
       <c r="G14" s="1">
-        <v>0.050105992704629898</v>
+        <v>0.1029641255736351</v>
       </c>
       <c r="H14" s="1"/>
       <c r="I14" t="s">
@@ -492,22 +492,22 @@
         <v>30643644</v>
       </c>
       <c r="B15" s="2">
-        <v>496521509.52673632</v>
+        <v>220848269.20712969</v>
       </c>
       <c r="C15" s="2">
-        <v>1041958931791872</v>
+        <v>445460015742976</v>
       </c>
       <c r="D15" s="1">
         <v>0.99904429912567139</v>
       </c>
       <c r="E15" s="2">
-        <v>511003845.72833443</v>
+        <v>250159768.28518739</v>
       </c>
       <c r="F15" s="1">
-        <v>5494283</v>
+        <v>3384690.25</v>
       </c>
       <c r="G15" s="1">
-        <v>0.052534863352775574</v>
+        <v>0.11666455119848251</v>
       </c>
       <c r="H15" s="1"/>
       <c r="I15" t="s">
@@ -519,22 +519,22 @@
         <v>30643644</v>
       </c>
       <c r="B16" s="2">
-        <v>546812910.2642901</v>
+        <v>278192012.90719116</v>
       </c>
       <c r="C16" s="2">
-        <v>1148145555734528</v>
+        <v>484518481887232</v>
       </c>
       <c r="D16" s="1">
         <v>0.99920356273651123</v>
       </c>
       <c r="E16" s="2">
-        <v>557716201.90534723</v>
+        <v>281654826.67486173</v>
       </c>
       <c r="F16" s="1">
-        <v>5494283</v>
+        <v>3384690.25</v>
       </c>
       <c r="G16" s="1">
-        <v>0.059790723025798798</v>
+        <v>0.11835610866546631</v>
       </c>
       <c r="H16" s="1"/>
       <c r="I16" t="s">
@@ -546,22 +546,22 @@
         <v>30643644</v>
       </c>
       <c r="B17" s="2">
-        <v>592668909.58819914</v>
+        <v>295433464.59741861</v>
       </c>
       <c r="C17" s="2">
-        <v>1238976463634432</v>
+        <v>515726821556224</v>
       </c>
       <c r="D17" s="1">
         <v>0.9993097186088562</v>
       </c>
       <c r="E17" s="2">
-        <v>606008882.91858673</v>
+        <v>295725492.74961603</v>
       </c>
       <c r="F17" s="1">
-        <v>5494283</v>
+        <v>3384690.25</v>
       </c>
       <c r="G17" s="1">
-        <v>0.060086462646722794</v>
+        <v>0.12303254008293152</v>
       </c>
       <c r="H17" s="1"/>
       <c r="I17" t="s">
@@ -573,22 +573,22 @@
         <v>30643644</v>
       </c>
       <c r="B18" s="2">
-        <v>649700742.47080517</v>
+        <v>303624036.877689</v>
       </c>
       <c r="C18" s="2">
-        <v>1354096887988224</v>
+        <v>555739340865536</v>
       </c>
       <c r="D18" s="1">
         <v>0.99941593408584595</v>
       </c>
       <c r="E18" s="2">
-        <v>667586924.40073753</v>
+        <v>314770068.2237246</v>
       </c>
       <c r="F18" s="1">
-        <v>5494283</v>
+        <v>3384690.25</v>
       </c>
       <c r="G18" s="1">
-        <v>0.057635478675365448</v>
+        <v>0.12332677841186523</v>
       </c>
       <c r="H18" s="1"/>
       <c r="I18" t="s">
@@ -600,22 +600,22 @@
         <v>30643644</v>
       </c>
       <c r="B19" s="2">
-        <v>726983503.38045478</v>
+        <v>327176642.28641671</v>
       </c>
       <c r="C19" s="2">
-        <v>1506654663213056</v>
+        <v>609288087142400</v>
       </c>
       <c r="D19" s="1">
         <v>0.99952214956283569</v>
       </c>
       <c r="E19" s="2">
-        <v>750391569.76029491</v>
+        <v>330099626.92071289</v>
       </c>
       <c r="F19" s="1">
-        <v>5494283</v>
+        <v>3384690.25</v>
       </c>
       <c r="G19" s="1">
-        <v>0.054105959832668305</v>
+        <v>0.12183916568756104</v>
       </c>
       <c r="H19" s="1"/>
       <c r="I19" t="s">
@@ -627,22 +627,22 @@
         <v>30643644</v>
       </c>
       <c r="B20" s="2">
-        <v>829662129.68653965</v>
+        <v>366038705.5931161</v>
       </c>
       <c r="C20" s="2">
-        <v>1722729904472064</v>
+        <v>689056165920768</v>
       </c>
       <c r="D20" s="1">
         <v>0.99962836503982544</v>
       </c>
       <c r="E20" s="2">
-        <v>866486135.83282113</v>
+        <v>376153681.9299323</v>
       </c>
       <c r="F20" s="1">
-        <v>5494283</v>
+        <v>3384690.25</v>
       </c>
       <c r="G20" s="1">
-        <v>0.05522579699754715</v>
+        <v>0.12712568044662476</v>
       </c>
       <c r="H20" s="1"/>
       <c r="I20" t="s">
@@ -654,22 +654,22 @@
         <v>30643644</v>
       </c>
       <c r="B21" s="2">
-        <v>1000166070.6822373</v>
+        <v>431011827.28948969</v>
       </c>
       <c r="C21" s="2">
-        <v>2065227373871104</v>
+        <v>814217150070784</v>
       </c>
       <c r="D21" s="1">
         <v>0.99973452091217041</v>
       </c>
       <c r="E21" s="2">
-        <v>1073388083.2821141</v>
+        <v>464651981.86846948</v>
       </c>
       <c r="F21" s="1">
-        <v>5494283</v>
+        <v>3384690.25</v>
       </c>
       <c r="G21" s="1">
-        <v>0.053384914994239807</v>
+        <v>0.12336988747119904</v>
       </c>
       <c r="H21" s="1"/>
       <c r="I21" t="s">
@@ -681,22 +681,22 @@
         <v>30643644</v>
       </c>
       <c r="B22" s="2">
-        <v>1378886628.1499693</v>
+        <v>587364275.96803951</v>
       </c>
       <c r="C22" s="2">
-        <v>2726453560999936</v>
+        <v>1047260666265600</v>
       </c>
       <c r="D22" s="1">
         <v>0.99984073638916016</v>
       </c>
       <c r="E22" s="2">
-        <v>2726453543.5949602</v>
+        <v>1047260634.7930751</v>
       </c>
       <c r="F22" s="1">
-        <v>5494283</v>
+        <v>3384690.25</v>
       </c>
       <c r="G22" s="1">
-        <v>0.042943686246871948</v>
+        <v>0.10602042824029922</v>
       </c>
       <c r="H22" s="1"/>
       <c r="I22" t="s">
@@ -746,22 +746,22 @@
         <v>37511548</v>
       </c>
       <c r="B2" s="2">
-        <v>4662836.7842122289</v>
+        <v>4295378.5182788745</v>
       </c>
       <c r="C2" s="2">
-        <v>132700488859648</v>
+        <v>79137347731456</v>
       </c>
       <c r="D2" s="1">
         <v>0.84004455804824829</v>
       </c>
       <c r="E2" s="2">
-        <v>14257357.76899391</v>
+        <v>13325757.718161672</v>
       </c>
       <c r="F2" s="1">
-        <v>21230356</v>
+        <v>12661542</v>
       </c>
       <c r="G2" s="1">
-        <v>0.00034965723170898855</v>
+        <v>0.0003720447130035609</v>
       </c>
       <c r="H2" s="1">
         <v>2023</v>
@@ -775,22 +775,22 @@
         <v>37511548</v>
       </c>
       <c r="B3" s="2">
-        <v>21474565.757624656</v>
+        <v>20105088.268517021</v>
       </c>
       <c r="C3" s="2">
-        <v>140657410703360</v>
+        <v>83558521634816</v>
       </c>
       <c r="D3" s="1">
         <v>0.85011380910873413</v>
       </c>
       <c r="E3" s="2">
-        <v>27053114.069536157</v>
+        <v>25214399.688844986</v>
       </c>
       <c r="F3" s="1">
-        <v>21230356</v>
+        <v>12661542</v>
       </c>
       <c r="G3" s="1">
-        <v>1.7376507457811385e-05</v>
+        <v>1.8648846889846027e-05</v>
       </c>
       <c r="H3" s="1"/>
       <c r="I3" t="s">
@@ -802,22 +802,22 @@
         <v>37511548</v>
       </c>
       <c r="B4" s="2">
-        <v>32337855.435309321</v>
+        <v>30011183.037156709</v>
       </c>
       <c r="C4" s="2">
-        <v>148695223894016</v>
+        <v>87686530465792</v>
       </c>
       <c r="D4" s="1">
         <v>0.86001795530319214</v>
       </c>
       <c r="E4" s="2">
-        <v>36718136.69807598</v>
+        <v>34083646.461425744</v>
       </c>
       <c r="F4" s="1">
-        <v>21230356</v>
+        <v>12661542</v>
       </c>
       <c r="G4" s="1">
-        <v>1.4008140169607941e-05</v>
+        <v>1.5418081602547318e-05</v>
       </c>
       <c r="H4" s="1"/>
       <c r="I4" t="s">
@@ -829,22 +829,22 @@
         <v>37511548</v>
       </c>
       <c r="B5" s="2">
-        <v>41027768.82239382</v>
+        <v>38096710.907335907</v>
       </c>
       <c r="C5" s="2">
-        <v>157374010621952</v>
+        <v>91862220144640</v>
       </c>
       <c r="D5" s="1">
-        <v>0.87008684873580933</v>
+        <v>0.87013453245162964</v>
       </c>
       <c r="E5" s="2">
-        <v>44598343.763534859</v>
+        <v>41268127.665194184</v>
       </c>
       <c r="F5" s="1">
-        <v>21230356</v>
+        <v>12661542</v>
       </c>
       <c r="G5" s="1">
-        <v>9.9256300018168986e-05</v>
+        <v>0.00011882751277880743</v>
       </c>
       <c r="H5" s="1"/>
       <c r="I5" t="s">
@@ -856,22 +856,22 @@
         <v>37511548</v>
       </c>
       <c r="B6" s="2">
-        <v>48022929.870814659</v>
+        <v>44102685.149156943</v>
       </c>
       <c r="C6" s="2">
-        <v>166812167700480</v>
+        <v>96033405140992</v>
       </c>
       <c r="D6" s="1">
-        <v>0.88011956214904785</v>
+        <v>0.88002568483352661</v>
       </c>
       <c r="E6" s="2">
-        <v>51387506.454848267</v>
+        <v>46738307.403743953</v>
       </c>
       <c r="F6" s="1">
-        <v>21230356</v>
+        <v>12661542</v>
       </c>
       <c r="G6" s="1">
-        <v>0.00066967139719054103</v>
+        <v>0.00074602977838367224</v>
       </c>
       <c r="H6" s="1"/>
       <c r="I6" t="s">
@@ -883,22 +883,22 @@
         <v>37511548</v>
       </c>
       <c r="B7" s="2">
-        <v>54917658.54052309</v>
+        <v>49646149.232012928</v>
       </c>
       <c r="C7" s="2">
-        <v>177249005338624</v>
+        <v>100581305745408</v>
       </c>
       <c r="D7" s="1">
-        <v>0.89006048440933228</v>
+        <v>0.89015942811965942</v>
       </c>
       <c r="E7" s="2">
-        <v>58250753.697320141</v>
+        <v>51784485.559176557</v>
       </c>
       <c r="F7" s="1">
-        <v>21230356</v>
+        <v>12661542</v>
       </c>
       <c r="G7" s="1">
-        <v>0.00094287260435521603</v>
+        <v>0.0010507331462576985</v>
       </c>
       <c r="H7" s="1"/>
       <c r="I7" t="s">
@@ -910,22 +910,22 @@
         <v>37511548</v>
       </c>
       <c r="B8" s="2">
-        <v>61323226.600192986</v>
+        <v>53654208.995983936</v>
       </c>
       <c r="C8" s="2">
-        <v>189246560272384</v>
+        <v>105462343139328</v>
       </c>
       <c r="D8" s="1">
-        <v>0.90012955665588379</v>
+        <v>0.90014749765396118</v>
       </c>
       <c r="E8" s="2">
-        <v>64273447.846717388</v>
+        <v>55946909.044118449</v>
       </c>
       <c r="F8" s="1">
-        <v>21230356</v>
+        <v>12661542</v>
       </c>
       <c r="G8" s="1">
-        <v>0.0012243612436577678</v>
+        <v>0.001464325818233192</v>
       </c>
       <c r="H8" s="1"/>
       <c r="I8" t="s">
@@ -937,22 +937,22 @@
         <v>37511548</v>
       </c>
       <c r="B9" s="2">
-        <v>67507909.826776758</v>
+        <v>58269942.783255212</v>
       </c>
       <c r="C9" s="2">
-        <v>203005689331712</v>
+        <v>110907480866816</v>
       </c>
       <c r="D9" s="1">
-        <v>0.91003447771072388</v>
+        <v>0.91004019975662232</v>
       </c>
       <c r="E9" s="2">
-        <v>71009180.913755044</v>
+        <v>60535978.837588996</v>
       </c>
       <c r="F9" s="1">
-        <v>21230356</v>
+        <v>12661542</v>
       </c>
       <c r="G9" s="1">
-        <v>0.0019093587761744857</v>
+        <v>0.0022470427211374045</v>
       </c>
       <c r="H9" s="1"/>
       <c r="I9" t="s">
@@ -964,22 +964,22 @@
         <v>37511548</v>
       </c>
       <c r="B10" s="2">
-        <v>74874444.336882859</v>
+        <v>63016207.391865723</v>
       </c>
       <c r="C10" s="2">
-        <v>219642312261632</v>
+        <v>117259502616576</v>
       </c>
       <c r="D10" s="1">
-        <v>0.92010438442230225</v>
+        <v>0.92011409997940063</v>
       </c>
       <c r="E10" s="2">
-        <v>78832351.597300932</v>
+        <v>65415643.928801403</v>
       </c>
       <c r="F10" s="1">
-        <v>21230356</v>
+        <v>12661542</v>
       </c>
       <c r="G10" s="1">
-        <v>0.0029802171047776937</v>
+        <v>0.0036045697052031756</v>
       </c>
       <c r="H10" s="1"/>
       <c r="I10" t="s">
@@ -991,22 +991,22 @@
         <v>37511548</v>
       </c>
       <c r="B11" s="2">
-        <v>83204483.797796503</v>
+        <v>67882343.603807077</v>
       </c>
       <c r="C11" s="2">
-        <v>239568443932672</v>
+        <v>124589183074304</v>
       </c>
       <c r="D11" s="1">
-        <v>0.93000888824462891</v>
+        <v>0.93000936508178711</v>
       </c>
       <c r="E11" s="2">
-        <v>88071942.513793722</v>
+        <v>71388565.451334193</v>
       </c>
       <c r="F11" s="1">
-        <v>21230356</v>
+        <v>12661542</v>
       </c>
       <c r="G11" s="1">
-        <v>0.0049323155544698238</v>
+        <v>0.0062407618388533592</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" t="s">
@@ -1018,22 +1018,22 @@
         <v>37511548</v>
       </c>
       <c r="B12" s="2">
-        <v>93366830.2434306</v>
+        <v>74482063.86772573</v>
       </c>
       <c r="C12" s="2">
-        <v>265025453293568</v>
+        <v>133527236509696</v>
       </c>
       <c r="D12" s="1">
-        <v>0.94007796049118042</v>
+        <v>0.94007682800292969</v>
       </c>
       <c r="E12" s="2">
-        <v>99299338.073882699</v>
+        <v>77903666.131064564</v>
       </c>
       <c r="F12" s="1">
-        <v>21230356</v>
+        <v>12661542</v>
       </c>
       <c r="G12" s="1">
-        <v>0.008396591991186142</v>
+        <v>0.010616962797939777</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" t="s">
@@ -1045,22 +1045,22 @@
         <v>37511548</v>
       </c>
       <c r="B13" s="2">
-        <v>106118344.74406588</v>
+        <v>82098558.297048867</v>
       </c>
       <c r="C13" s="2">
-        <v>298500998823936</v>
+        <v>144763768537088</v>
       </c>
       <c r="D13" s="1">
-        <v>0.95014780759811401</v>
+        <v>0.95014756917953491</v>
       </c>
       <c r="E13" s="2">
-        <v>114443677.99995156</v>
+        <v>87133031.296933293</v>
       </c>
       <c r="F13" s="1">
-        <v>21230356</v>
+        <v>12661542</v>
       </c>
       <c r="G13" s="1">
-        <v>0.013120471499860287</v>
+        <v>0.017254123464226723</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" t="s">
@@ -1072,22 +1072,22 @@
         <v>37511548</v>
       </c>
       <c r="B14" s="2">
-        <v>123993595.73436743</v>
+        <v>91422693.78531073</v>
       </c>
       <c r="C14" s="2">
-        <v>344135194116096</v>
+        <v>159052705300480</v>
       </c>
       <c r="D14" s="1">
         <v>0.96005219221115112</v>
       </c>
       <c r="E14" s="2">
-        <v>135123131.46636164</v>
+        <v>96830990.384717196</v>
       </c>
       <c r="F14" s="1">
-        <v>21230356</v>
+        <v>12661542</v>
       </c>
       <c r="G14" s="1">
-        <v>0.016330795362591744</v>
+        <v>0.022789968177676201</v>
       </c>
       <c r="H14" s="1"/>
       <c r="I14" t="s">
@@ -1099,22 +1099,22 @@
         <v>37511548</v>
       </c>
       <c r="B15" s="2">
-        <v>147357684.13391557</v>
+        <v>101579340.64870097</v>
       </c>
       <c r="C15" s="2">
-        <v>414576248094720</v>
+        <v>180023201890304</v>
       </c>
       <c r="D15" s="1">
-        <v>0.97012174129486084</v>
+        <v>0.97012192010879517</v>
       </c>
       <c r="E15" s="2">
-        <v>166294402.24638048</v>
+        <v>116476777.89680797</v>
       </c>
       <c r="F15" s="1">
-        <v>21230356</v>
+        <v>12661542</v>
       </c>
       <c r="G15" s="1">
-        <v>0.025105981156229973</v>
+        <v>0.035790335386991501</v>
       </c>
       <c r="H15" s="1"/>
       <c r="I15" t="s">
@@ -1126,22 +1126,22 @@
         <v>37511548</v>
       </c>
       <c r="B16" s="2">
-        <v>191436145.51033592</v>
+        <v>130444348.07878588</v>
       </c>
       <c r="C16" s="2">
-        <v>537692223832064</v>
+        <v>211533112016896</v>
       </c>
       <c r="D16" s="1">
-        <v>0.98002618551254272</v>
+        <v>0.98002612590789795</v>
       </c>
       <c r="E16" s="2">
-        <v>235208702.67315114</v>
+        <v>149966222.17427331</v>
       </c>
       <c r="F16" s="1">
-        <v>21230356</v>
+        <v>12661542</v>
       </c>
       <c r="G16" s="1">
-        <v>0.043693892657756806</v>
+        <v>0.068645939230918884</v>
       </c>
       <c r="H16" s="1"/>
       <c r="I16" t="s">
@@ -1153,22 +1153,22 @@
         <v>37511548</v>
       </c>
       <c r="B17" s="2">
-        <v>300334104.02196735</v>
+        <v>173898208.84441569</v>
       </c>
       <c r="C17" s="2">
-        <v>845215405441024</v>
+        <v>274124576391168</v>
       </c>
       <c r="D17" s="1">
-        <v>0.99009561538696289</v>
+        <v>0.99009549617767334</v>
       </c>
       <c r="E17" s="2">
-        <v>308572219.70716482</v>
+        <v>175763615.62474772</v>
       </c>
       <c r="F17" s="1">
-        <v>21230356</v>
+        <v>12661542</v>
       </c>
       <c r="G17" s="1">
-        <v>0.052504267543554306</v>
+        <v>0.091787993907928467</v>
       </c>
       <c r="H17" s="1"/>
       <c r="I17" t="s">
@@ -1180,22 +1180,22 @@
         <v>37511548</v>
       </c>
       <c r="B18" s="2">
-        <v>320810478.03617573</v>
+        <v>178113872.41602066</v>
       </c>
       <c r="C18" s="2">
-        <v>904844382568448</v>
+        <v>285055402377216</v>
       </c>
       <c r="D18" s="1">
         <v>0.99108606576919556</v>
       </c>
       <c r="E18" s="2">
-        <v>330861357.26205862</v>
+        <v>180837378.84253031</v>
       </c>
       <c r="F18" s="1">
-        <v>21230356</v>
+        <v>12661542</v>
       </c>
       <c r="G18" s="1">
-        <v>0.052570827305316925</v>
+        <v>0.097511395812034607</v>
       </c>
       <c r="H18" s="1"/>
       <c r="I18" t="s">
@@ -1207,22 +1207,22 @@
         <v>37511548</v>
       </c>
       <c r="B19" s="2">
-        <v>345909765.54174066</v>
+        <v>185519854.30463576</v>
       </c>
       <c r="C19" s="2">
-        <v>976590603288576</v>
+        <v>298081534869504</v>
       </c>
       <c r="D19" s="1">
-        <v>0.99207651615142822</v>
+        <v>0.99207645654678345</v>
       </c>
       <c r="E19" s="2">
-        <v>358092013.59280789</v>
+        <v>186279047.2371006</v>
       </c>
       <c r="F19" s="1">
-        <v>21230356</v>
+        <v>12661542</v>
       </c>
       <c r="G19" s="1">
-        <v>0.05350099503993988</v>
+        <v>0.1012779101729393</v>
       </c>
       <c r="H19" s="1"/>
       <c r="I19" t="s">
@@ -1234,22 +1234,22 @@
         <v>37511548</v>
       </c>
       <c r="B20" s="2">
-        <v>376411327.89796579</v>
+        <v>189750034.40478113</v>
       </c>
       <c r="C20" s="2">
-        <v>1064945126998016</v>
+        <v>314053276729344</v>
       </c>
       <c r="D20" s="1">
         <v>0.99306690692901611</v>
       </c>
       <c r="E20" s="2">
-        <v>391355424.82639825</v>
+        <v>192863618.20432767</v>
       </c>
       <c r="F20" s="1">
-        <v>21230356</v>
+        <v>12661542</v>
       </c>
       <c r="G20" s="1">
-        <v>0.053109142929315567</v>
+        <v>0.10941072553396225</v>
       </c>
       <c r="H20" s="1"/>
       <c r="I20" t="s">
@@ -1261,22 +1261,22 @@
         <v>37511548</v>
       </c>
       <c r="B21" s="2">
-        <v>414086030.84625322</v>
+        <v>198085730.45865637</v>
       </c>
       <c r="C21" s="2">
-        <v>1177213760176128</v>
+        <v>334253346783232</v>
       </c>
       <c r="D21" s="1">
-        <v>0.99405735731124878</v>
+        <v>0.99405741691589355</v>
       </c>
       <c r="E21" s="2">
-        <v>433577243.10284501</v>
+        <v>200459202.00010756</v>
       </c>
       <c r="F21" s="1">
-        <v>21230356</v>
+        <v>12661542</v>
       </c>
       <c r="G21" s="1">
-        <v>0.054989688098430634</v>
+        <v>0.11711125075817108</v>
       </c>
       <c r="H21" s="1"/>
       <c r="I21" t="s">
@@ -1288,22 +1288,22 @@
         <v>37511548</v>
       </c>
       <c r="B22" s="2">
-        <v>463355810.7540772</v>
+        <v>203896962.69379848</v>
       </c>
       <c r="C22" s="2">
-        <v>1325941766750208</v>
+        <v>361051359019008</v>
       </c>
       <c r="D22" s="1">
-        <v>0.99504780769348145</v>
+        <v>0.99504905939102173</v>
       </c>
       <c r="E22" s="2">
-        <v>486943865.31007743</v>
+        <v>213652105.39506304</v>
       </c>
       <c r="F22" s="1">
-        <v>21230356</v>
+        <v>12661542</v>
       </c>
       <c r="G22" s="1">
-        <v>0.052925065159797669</v>
+        <v>0.12037795037031174</v>
       </c>
       <c r="H22" s="1"/>
       <c r="I22" t="s">
@@ -1315,22 +1315,22 @@
         <v>37511548</v>
       </c>
       <c r="B23" s="2">
-        <v>524994961.56951398</v>
+        <v>248820587.1144841</v>
       </c>
       <c r="C23" s="2">
-        <v>1535685689344000</v>
+        <v>397857047707648</v>
       </c>
       <c r="D23" s="1">
         <v>0.99603825807571411</v>
       </c>
       <c r="E23" s="2">
-        <v>567539995.72039938</v>
+        <v>256299772.01152054</v>
       </c>
       <c r="F23" s="1">
-        <v>21230356</v>
+        <v>12661542</v>
       </c>
       <c r="G23" s="1">
-        <v>0.060783930122852326</v>
+        <v>0.13517048954963684</v>
       </c>
       <c r="H23" s="1"/>
       <c r="I23" t="s">
@@ -1342,22 +1342,22 @@
         <v>37511548</v>
       </c>
       <c r="B24" s="2">
-        <v>638613094.94590664</v>
+        <v>268997368.8034879</v>
       </c>
       <c r="C24" s="2">
-        <v>1858400807813120</v>
+        <v>445040283353088</v>
       </c>
       <c r="D24" s="1">
         <v>0.997028648853302</v>
       </c>
       <c r="E24" s="2">
-        <v>713425516.95645154</v>
+        <v>275139474.61915261</v>
       </c>
       <c r="F24" s="1">
-        <v>21230356</v>
+        <v>12661542</v>
       </c>
       <c r="G24" s="1">
-        <v>0.057759139686822891</v>
+        <v>0.14887738227844238</v>
       </c>
       <c r="H24" s="1"/>
       <c r="I24" t="s">
@@ -1369,22 +1369,22 @@
         <v>37511548</v>
       </c>
       <c r="B25" s="2">
-        <v>846954833.17183459</v>
+        <v>283284882.1059432</v>
       </c>
       <c r="C25" s="2">
-        <v>2430911492653056</v>
+        <v>529994098933760</v>
       </c>
       <c r="D25" s="1">
         <v>0.99801915884017944</v>
       </c>
       <c r="E25" s="2">
-        <v>1024393968.4547682</v>
+        <v>308212044.24945492</v>
       </c>
       <c r="F25" s="1">
-        <v>21230356</v>
+        <v>12661542</v>
       </c>
       <c r="G25" s="1">
-        <v>0.048307400196790695</v>
+        <v>0.1596243679523468</v>
       </c>
       <c r="H25" s="1"/>
       <c r="I25" t="s">
@@ -1396,22 +1396,22 @@
         <v>37511548</v>
       </c>
       <c r="B26" s="2">
-        <v>1410917421.1886306</v>
+        <v>367022768.41085273</v>
       </c>
       <c r="C26" s="2">
-        <v>3837466842759168</v>
+        <v>751782150012928</v>
       </c>
       <c r="D26" s="1">
         <v>0.99900960922241211</v>
       </c>
       <c r="E26" s="2">
-        <v>1518891275.2745478</v>
+        <v>377117314.59948307</v>
       </c>
       <c r="F26" s="1">
-        <v>21230356</v>
+        <v>12661542</v>
       </c>
       <c r="G26" s="1">
-        <v>0.04338005930185318</v>
+        <v>0.17424716055393219</v>
       </c>
       <c r="H26" s="1"/>
       <c r="I26" t="s">
@@ -1423,22 +1423,22 @@
         <v>37511548</v>
       </c>
       <c r="B27" s="2">
-        <v>1943854189.1149871</v>
+        <v>404330895.18733865</v>
       </c>
       <c r="C27" s="2">
-        <v>4996754214748160</v>
+        <v>939114463494144</v>
       </c>
       <c r="D27" s="1">
         <v>0.99933969974517822</v>
       </c>
       <c r="E27" s="2">
-        <v>2213627321.8669252</v>
+        <v>435874391.14987081</v>
       </c>
       <c r="F27" s="1">
-        <v>21230356</v>
+        <v>12661542</v>
       </c>
       <c r="G27" s="1">
-        <v>0.034828528761863708</v>
+        <v>0.17587555944919586</v>
       </c>
       <c r="H27" s="1"/>
       <c r="I27" t="s">
@@ -1450,22 +1450,22 @@
         <v>37511548</v>
       </c>
       <c r="B28" s="2">
-        <v>3592650706.23385</v>
+        <v>587082498.86950934</v>
       </c>
       <c r="C28" s="2">
-        <v>7779881748267008</v>
+        <v>1442354707824640</v>
       </c>
       <c r="D28" s="1">
         <v>0.99966984987258911</v>
       </c>
       <c r="E28" s="2">
-        <v>7779882295.865633</v>
+        <v>1442354686.6925068</v>
       </c>
       <c r="F28" s="1">
-        <v>21230356</v>
+        <v>12661542</v>
       </c>
       <c r="G28" s="1">
-        <v>0.023982319980859757</v>
+        <v>0.13831782341003418</v>
       </c>
       <c r="H28" s="1"/>
       <c r="I28" t="s">
@@ -1515,22 +1515,22 @@
         <v>31247746</v>
       </c>
       <c r="B2" s="2">
-        <v>31220802.177000001</v>
+        <v>29283843.899840169</v>
       </c>
       <c r="C2" s="2">
-        <v>121093583011840</v>
+        <v>76893453811712</v>
       </c>
       <c r="D2" s="1">
-        <v>0.9500313401222229</v>
+        <v>0.95004945993423462</v>
       </c>
       <c r="E2" s="2">
-        <v>40402066.538375929</v>
+        <v>34587591.062042482</v>
       </c>
       <c r="F2" s="1">
-        <v>6207971</v>
+        <v>3981268.75</v>
       </c>
       <c r="G2" s="1">
-        <v>0.0033773905597627163</v>
+        <v>0.0039304639212787151</v>
       </c>
       <c r="H2" s="1">
         <v>2015</v>
@@ -1544,22 +1544,22 @@
         <v>31247746</v>
       </c>
       <c r="B3" s="2">
-        <v>48224645.508337818</v>
+        <v>39338353.02525013</v>
       </c>
       <c r="C3" s="2">
-        <v>141305179013120</v>
+        <v>87469450067968</v>
       </c>
       <c r="D3" s="1">
-        <v>0.9600403904914856</v>
+        <v>0.96003925800323486</v>
       </c>
       <c r="E3" s="2">
-        <v>57185109.623485789</v>
+        <v>44585174.003409646</v>
       </c>
       <c r="F3" s="1">
-        <v>6207971</v>
+        <v>3981268.75</v>
       </c>
       <c r="G3" s="1">
-        <v>0.0070269596762955189</v>
+        <v>0.0090544437989592552</v>
       </c>
       <c r="H3" s="1"/>
       <c r="I3" t="s">
@@ -1571,22 +1571,22 @@
         <v>31247746</v>
       </c>
       <c r="B4" s="2">
-        <v>67885969.379421219</v>
+        <v>50846224.500809498</v>
       </c>
       <c r="C4" s="2">
-        <v>169400472698880</v>
+        <v>101811134398464</v>
       </c>
       <c r="D4" s="1">
-        <v>0.97004508972167969</v>
+        <v>0.97005397081375122</v>
       </c>
       <c r="E4" s="2">
-        <v>80683354.244405523</v>
+        <v>58840529.298668101</v>
       </c>
       <c r="F4" s="1">
-        <v>6207971</v>
+        <v>3981268.75</v>
       </c>
       <c r="G4" s="1">
-        <v>0.015729565173387527</v>
+        <v>0.021705092862248421</v>
       </c>
       <c r="H4" s="1"/>
       <c r="I4" t="s">
@@ -1598,22 +1598,22 @@
         <v>31247746</v>
       </c>
       <c r="B5" s="2">
-        <v>94377000.535618633</v>
+        <v>66381885.193133041</v>
       </c>
       <c r="C5" s="2">
-        <v>213891384606720</v>
+        <v>123340379389952</v>
       </c>
       <c r="D5" s="1">
-        <v>0.98004990816116333</v>
+        <v>0.98004961013793945</v>
       </c>
       <c r="E5" s="2">
-        <v>112922640.41501835</v>
+        <v>77839468.95030427</v>
       </c>
       <c r="F5" s="1">
-        <v>6207971</v>
+        <v>3981268.75</v>
       </c>
       <c r="G5" s="1">
-        <v>0.026283815503120422</v>
+        <v>0.037994083017110825</v>
       </c>
       <c r="H5" s="1"/>
       <c r="I5" t="s">
@@ -1625,22 +1625,22 @@
         <v>31247746</v>
       </c>
       <c r="B6" s="2">
-        <v>140603846.74139786</v>
+        <v>96163539.901718587</v>
       </c>
       <c r="C6" s="2">
-        <v>315467059167232</v>
+        <v>169122574893056</v>
       </c>
       <c r="D6" s="1">
-        <v>0.99005484580993652</v>
+        <v>0.99005556106567383</v>
       </c>
       <c r="E6" s="2">
-        <v>144710059.13493449</v>
+        <v>98184330.705767661</v>
       </c>
       <c r="F6" s="1">
-        <v>6207971</v>
+        <v>3981268.75</v>
       </c>
       <c r="G6" s="1">
-        <v>0.035859253257513046</v>
+        <v>0.052692737430334091</v>
       </c>
       <c r="H6" s="1"/>
       <c r="I6" t="s">
@@ -1652,22 +1652,22 @@
         <v>31247746</v>
       </c>
       <c r="B7" s="2">
-        <v>149659625.53705692</v>
+        <v>100034927.06344086</v>
       </c>
       <c r="C7" s="2">
-        <v>333557998288896</v>
+        <v>176633717719040</v>
       </c>
       <c r="D7" s="1">
-        <v>0.99100756645202637</v>
+        <v>0.99100768566131592</v>
       </c>
       <c r="E7" s="2">
-        <v>154851950.22283331</v>
+        <v>102560666.01385044</v>
       </c>
       <c r="F7" s="1">
-        <v>6207971</v>
+        <v>3981268.75</v>
       </c>
       <c r="G7" s="1">
-        <v>0.037392299622297287</v>
+        <v>0.056756366044282913</v>
       </c>
       <c r="H7" s="1"/>
       <c r="I7" t="s">
@@ -1679,22 +1679,22 @@
         <v>31247746</v>
       </c>
       <c r="B8" s="2">
-        <v>161135838.62291554</v>
+        <v>104876247.98711756</v>
       </c>
       <c r="C8" s="2">
-        <v>356232003059712</v>
+        <v>186075716780032</v>
       </c>
       <c r="D8" s="1">
-        <v>0.99202001094818115</v>
+        <v>0.99202430248260498</v>
       </c>
       <c r="E8" s="2">
-        <v>167488438.6462146</v>
+        <v>107607508.93002979</v>
       </c>
       <c r="F8" s="1">
-        <v>6207971</v>
+        <v>3981268.75</v>
       </c>
       <c r="G8" s="1">
-        <v>0.039710354059934616</v>
+        <v>0.060980472713708878</v>
       </c>
       <c r="H8" s="1"/>
       <c r="I8" t="s">
@@ -1706,22 +1706,22 @@
         <v>31247746</v>
       </c>
       <c r="B9" s="2">
-        <v>175276341.76533908</v>
+        <v>111833293.45493564</v>
       </c>
       <c r="C9" s="2">
-        <v>383656543649792</v>
+        <v>197445803835392</v>
       </c>
       <c r="D9" s="1">
-        <v>0.99303239583969116</v>
+        <v>0.993033766746521</v>
       </c>
       <c r="E9" s="2">
-        <v>183194761.49546361</v>
+        <v>114768281.8574051</v>
       </c>
       <c r="F9" s="1">
-        <v>6207971</v>
+        <v>3981268.75</v>
       </c>
       <c r="G9" s="1">
-        <v>0.040648102760314942</v>
+        <v>0.065254814922809601</v>
       </c>
       <c r="H9" s="1"/>
       <c r="I9" t="s">
@@ -1733,22 +1733,22 @@
         <v>31247746</v>
       </c>
       <c r="B10" s="2">
-        <v>192867140.70891514</v>
+        <v>117928846.77419357</v>
       </c>
       <c r="C10" s="2">
-        <v>417732948393984</v>
+        <v>211482411270144</v>
       </c>
       <c r="D10" s="1">
         <v>0.99404478073120117</v>
       </c>
       <c r="E10" s="2">
-        <v>203045334.50663796</v>
+        <v>123223396.93937093</v>
       </c>
       <c r="F10" s="1">
-        <v>6207971</v>
+        <v>3981268.75</v>
       </c>
       <c r="G10" s="1">
-        <v>0.043097231537103653</v>
+        <v>0.071104064583778381</v>
       </c>
       <c r="H10" s="1"/>
       <c r="I10" t="s">
@@ -1760,22 +1760,22 @@
         <v>31247746</v>
       </c>
       <c r="B11" s="2">
-        <v>215764506.19278407</v>
+        <v>130444057.65086208</v>
       </c>
       <c r="C11" s="2">
-        <v>461706836836352</v>
+        <v>229559710515200</v>
       </c>
       <c r="D11" s="1">
         <v>0.99505716562271118</v>
       </c>
       <c r="E11" s="2">
-        <v>228645850.08431312</v>
+        <v>136023464.55076408</v>
       </c>
       <c r="F11" s="1">
-        <v>6207971</v>
+        <v>3981268.75</v>
       </c>
       <c r="G11" s="1">
-        <v>0.045526504516601563</v>
+        <v>0.076285228133201599</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" t="s">
@@ -1787,22 +1787,22 @@
         <v>31247746</v>
       </c>
       <c r="B12" s="2">
-        <v>245063637.53351206</v>
+        <v>142642420.30048469</v>
       </c>
       <c r="C12" s="2">
-        <v>517354245062656</v>
+        <v>251897768312832</v>
       </c>
       <c r="D12" s="1">
-        <v>0.99600988626480103</v>
+        <v>0.99601006507873535</v>
       </c>
       <c r="E12" s="2">
-        <v>264700864.53057933</v>
+        <v>151758636.52593645</v>
       </c>
       <c r="F12" s="1">
-        <v>6207971</v>
+        <v>3981268.75</v>
       </c>
       <c r="G12" s="1">
-        <v>0.048756819218397141</v>
+        <v>0.08493737131357193</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" t="s">
@@ -1814,22 +1814,22 @@
         <v>31247746</v>
       </c>
       <c r="B13" s="2">
-        <v>289296711.98280495</v>
+        <v>161965197.31182799</v>
       </c>
       <c r="C13" s="2">
-        <v>603268287823872</v>
+        <v>285945869893632</v>
       </c>
       <c r="D13" s="1">
-        <v>0.99702239036560059</v>
+        <v>0.99702244997024536</v>
       </c>
       <c r="E13" s="2">
-        <v>319211590.6116643</v>
+        <v>172983629.82866538</v>
       </c>
       <c r="F13" s="1">
-        <v>6207971</v>
+        <v>3981268.75</v>
       </c>
       <c r="G13" s="1">
-        <v>0.0507613904774189</v>
+        <v>0.093359202146530151</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" t="s">
@@ -1841,22 +1841,22 @@
         <v>31247746</v>
       </c>
       <c r="B14" s="2">
-        <v>361146130.5749597</v>
+        <v>189784844.70714668</v>
       </c>
       <c r="C14" s="2">
-        <v>749603125198848</v>
+        <v>344137744252928</v>
       </c>
       <c r="D14" s="1">
         <v>0.9980347752571106</v>
       </c>
       <c r="E14" s="2">
-        <v>428014181.5554561</v>
+        <v>205905088.4311091</v>
       </c>
       <c r="F14" s="1">
-        <v>6207971</v>
+        <v>3981268.75</v>
       </c>
       <c r="G14" s="1">
-        <v>0.051412466913461685</v>
+        <v>0.10710126906633377</v>
       </c>
       <c r="H14" s="1"/>
       <c r="I14" t="s">
@@ -1868,22 +1868,22 @@
         <v>31247746</v>
       </c>
       <c r="B15" s="2">
-        <v>535273540.03224069</v>
+        <v>279532113.48253632</v>
       </c>
       <c r="C15" s="2">
-        <v>1135502916845568</v>
+        <v>510013944627200</v>
       </c>
       <c r="D15" s="1">
         <v>0.99910670518875122</v>
       </c>
       <c r="E15" s="2">
-        <v>546187766.52337456</v>
+        <v>280731670.38984418</v>
       </c>
       <c r="F15" s="1">
-        <v>6207971</v>
+        <v>3981268.75</v>
       </c>
       <c r="G15" s="1">
-        <v>0.062231332063674927</v>
+        <v>0.12102578580379486</v>
       </c>
       <c r="H15" s="1"/>
       <c r="I15" t="s">
@@ -1895,22 +1895,22 @@
         <v>31247746</v>
       </c>
       <c r="B16" s="2">
-        <v>580791148.3073616</v>
+        <v>295326295.0026868</v>
       </c>
       <c r="C16" s="2">
-        <v>1226174374084608</v>
+        <v>545291061166080</v>
       </c>
       <c r="D16" s="1">
         <v>0.99922585487365723</v>
       </c>
       <c r="E16" s="2">
-        <v>607749410.89020228</v>
+        <v>301617172.84614009</v>
       </c>
       <c r="F16" s="1">
-        <v>6207971</v>
+        <v>3981268.75</v>
       </c>
       <c r="G16" s="1">
-        <v>0.060031738132238388</v>
+        <v>0.1208764985203743</v>
       </c>
       <c r="H16" s="1"/>
       <c r="I16" t="s">
@@ -1922,22 +1922,22 @@
         <v>31247746</v>
       </c>
       <c r="B17" s="2">
-        <v>671079418.59215474</v>
+        <v>333931493.82052654</v>
       </c>
       <c r="C17" s="2">
-        <v>1411721793110016</v>
+        <v>618401068220416</v>
       </c>
       <c r="D17" s="1">
         <v>0.99940448999404907</v>
       </c>
       <c r="E17" s="2">
-        <v>691190180.54809237</v>
+        <v>338193661.47232676</v>
       </c>
       <c r="F17" s="1">
-        <v>6207971</v>
+        <v>3981268.75</v>
       </c>
       <c r="G17" s="1">
-        <v>0.062790066003799438</v>
+        <v>0.12827104330062866</v>
       </c>
       <c r="H17" s="1"/>
       <c r="I17" t="s">
@@ -1949,22 +1949,22 @@
         <v>31247746</v>
       </c>
       <c r="B18" s="2">
-        <v>761159524.19354844</v>
+        <v>345982411.29032266</v>
       </c>
       <c r="C18" s="2">
-        <v>1591878893961216</v>
+        <v>688462319583232</v>
       </c>
       <c r="D18" s="1">
         <v>0.99952363967895508</v>
       </c>
       <c r="E18" s="2">
-        <v>825128140.21855962</v>
+        <v>365361365.04836983</v>
       </c>
       <c r="F18" s="1">
-        <v>6207971</v>
+        <v>3981268.75</v>
       </c>
       <c r="G18" s="1">
-        <v>0.056957736611366272</v>
+        <v>0.12846976518630981</v>
       </c>
       <c r="H18" s="1"/>
       <c r="I18" t="s">
@@ -1976,22 +1976,22 @@
         <v>31247746</v>
       </c>
       <c r="B19" s="2">
-        <v>998646660.93498123</v>
+        <v>440276301.98817849</v>
       </c>
       <c r="C19" s="2">
-        <v>2051896466472960</v>
+        <v>882309024710656</v>
       </c>
       <c r="D19" s="1">
         <v>0.99970227479934692</v>
       </c>
       <c r="E19" s="2">
-        <v>1073344845.2444921</v>
+        <v>468089518.26974756</v>
       </c>
       <c r="F19" s="1">
-        <v>6207971</v>
+        <v>3981268.75</v>
       </c>
       <c r="G19" s="1">
-        <v>0.059331931173801422</v>
+        <v>0.13601958751678467</v>
       </c>
       <c r="H19" s="1"/>
       <c r="I19" t="s">
@@ -2003,22 +2003,22 @@
         <v>31247746</v>
       </c>
       <c r="B20" s="2">
-        <v>1392363112.8425577</v>
+        <v>603808807.63030613</v>
       </c>
       <c r="C20" s="2">
-        <v>2704381187194880</v>
+        <v>1158504882634752</v>
       </c>
       <c r="D20" s="1">
         <v>0.99982136487960816</v>
       </c>
       <c r="E20" s="2">
-        <v>2704381123.969903</v>
+        <v>1158504835.8538158</v>
       </c>
       <c r="F20" s="1">
-        <v>6207971</v>
+        <v>3981268.75</v>
       </c>
       <c r="G20" s="1">
-        <v>0.047024995088577271</v>
+        <v>0.10973061621189117</v>
       </c>
       <c r="H20" s="1"/>
       <c r="I20" t="s">
@@ -2068,22 +2068,22 @@
         <v>31890754</v>
       </c>
       <c r="B2" s="2">
-        <v>10883914.445399828</v>
+        <v>9288002.3201856129</v>
       </c>
       <c r="C2" s="2">
-        <v>111912469659648</v>
+        <v>73099806507008</v>
       </c>
       <c r="D2" s="1">
-        <v>0.94003432989120483</v>
+        <v>0.94003033638000488</v>
       </c>
       <c r="E2" s="2">
-        <v>26254068.515270431</v>
+        <v>23205799.354700934</v>
       </c>
       <c r="F2" s="1">
-        <v>6724635</v>
+        <v>4394902.5</v>
       </c>
       <c r="G2" s="1">
-        <v>0.0021987073123455048</v>
+        <v>0.0029292507097125054</v>
       </c>
       <c r="H2" s="1">
         <v>2016</v>
@@ -2097,22 +2097,22 @@
         <v>31890754</v>
       </c>
       <c r="B3" s="2">
-        <v>38329835.420393556</v>
+        <v>32521212.962962963</v>
       </c>
       <c r="C3" s="2">
-        <v>129016405164032</v>
+        <v>83109387173888</v>
       </c>
       <c r="D3" s="1">
-        <v>0.950015127658844</v>
+        <v>0.950050950050354</v>
       </c>
       <c r="E3" s="2">
-        <v>46028016.70025155</v>
+        <v>38367802.706662983</v>
       </c>
       <c r="F3" s="1">
-        <v>6724635</v>
+        <v>4394902.5</v>
       </c>
       <c r="G3" s="1">
-        <v>0.0035285218618810177</v>
+        <v>0.0043443599715828896</v>
       </c>
       <c r="H3" s="1"/>
       <c r="I3" t="s">
@@ -2124,22 +2124,22 @@
         <v>31890754</v>
       </c>
       <c r="B4" s="2">
-        <v>53261528.796241343</v>
+        <v>42667238.872403555</v>
       </c>
       <c r="C4" s="2">
-        <v>149862330925056</v>
+        <v>94305242841088</v>
       </c>
       <c r="D4" s="1">
-        <v>0.96005016565322876</v>
+        <v>0.96004825830459595</v>
       </c>
       <c r="E4" s="2">
-        <v>62533671.922689617</v>
+        <v>48161846.353572994</v>
       </c>
       <c r="F4" s="1">
-        <v>6724635</v>
+        <v>4394902.5</v>
       </c>
       <c r="G4" s="1">
-        <v>0.0075881709344685078</v>
+        <v>0.0097354501485824585</v>
       </c>
       <c r="H4" s="1"/>
       <c r="I4" t="s">
@@ -2151,22 +2151,22 @@
         <v>31890754</v>
       </c>
       <c r="B5" s="2">
-        <v>73344029.282266006</v>
+        <v>54489791.42300196</v>
       </c>
       <c r="C5" s="2">
-        <v>178910536925184</v>
+        <v>109679615148032</v>
       </c>
       <c r="D5" s="1">
-        <v>0.97002178430557251</v>
+        <v>0.97003287076950073</v>
       </c>
       <c r="E5" s="2">
-        <v>86103910.707819775</v>
+        <v>62087340.083673664</v>
       </c>
       <c r="F5" s="1">
-        <v>6724635</v>
+        <v>4394902.5</v>
       </c>
       <c r="G5" s="1">
-        <v>0.015410643070936203</v>
+        <v>0.021992329508066177</v>
       </c>
       <c r="H5" s="1"/>
       <c r="I5" t="s">
@@ -2178,22 +2178,22 @@
         <v>31890754</v>
       </c>
       <c r="B6" s="2">
-        <v>99590870.129838318</v>
+        <v>68137315.37320812</v>
       </c>
       <c r="C6" s="2">
-        <v>225605471698944</v>
+        <v>133615417556992</v>
       </c>
       <c r="D6" s="1">
-        <v>0.98005634546279907</v>
+        <v>0.98006093502044678</v>
       </c>
       <c r="E6" s="2">
-        <v>119064473.45516638</v>
+        <v>84259605.043867141</v>
       </c>
       <c r="F6" s="1">
-        <v>6724635</v>
+        <v>4394902.5</v>
       </c>
       <c r="G6" s="1">
-        <v>0.026116589084267616</v>
+        <v>0.036820512264966965</v>
       </c>
       <c r="H6" s="1"/>
       <c r="I6" t="s">
@@ -2205,22 +2205,22 @@
         <v>31890754</v>
       </c>
       <c r="B7" s="2">
-        <v>148308681.34586838</v>
+        <v>102462282.16074951</v>
       </c>
       <c r="C7" s="2">
-        <v>332153510428672</v>
+        <v>182950440206336</v>
       </c>
       <c r="D7" s="1">
-        <v>0.9900285005569458</v>
+        <v>0.99002838134765625</v>
       </c>
       <c r="E7" s="2">
-        <v>152793153.57029992</v>
+        <v>104067803.15343133</v>
       </c>
       <c r="F7" s="1">
-        <v>6724635</v>
+        <v>4394902.5</v>
       </c>
       <c r="G7" s="1">
-        <v>0.035265985876321793</v>
+        <v>0.051487904042005539</v>
       </c>
       <c r="H7" s="1"/>
       <c r="I7" t="s">
@@ -2232,22 +2232,22 @@
         <v>31890754</v>
       </c>
       <c r="B8" s="2">
-        <v>158214354.85460818</v>
+        <v>106311619.66236344</v>
       </c>
       <c r="C8" s="2">
-        <v>352504005001216</v>
+        <v>191914892591104</v>
       </c>
       <c r="D8" s="1">
-        <v>0.99104458093643188</v>
+        <v>0.99104595184326172</v>
       </c>
       <c r="E8" s="2">
-        <v>163560794.09683693</v>
+        <v>108524650.21607092</v>
       </c>
       <c r="F8" s="1">
-        <v>6724635</v>
+        <v>4394902.5</v>
       </c>
       <c r="G8" s="1">
-        <v>0.036791130900382996</v>
+        <v>0.054229471832513809</v>
       </c>
       <c r="H8" s="1"/>
       <c r="I8" t="s">
@@ -2259,22 +2259,22 @@
         <v>31890754</v>
       </c>
       <c r="B9" s="2">
-        <v>170059530.77301821</v>
+        <v>111231782.7160494</v>
       </c>
       <c r="C9" s="2">
-        <v>376686247936000</v>
+        <v>202576192602112</v>
       </c>
       <c r="D9" s="1">
-        <v>0.99206072092056274</v>
+        <v>0.99206089973449707</v>
       </c>
       <c r="E9" s="2">
-        <v>176252481.4396472</v>
+        <v>114737615.28850898</v>
       </c>
       <c r="F9" s="1">
-        <v>6724635</v>
+        <v>4394902.5</v>
       </c>
       <c r="G9" s="1">
-        <v>0.038856104016304016</v>
+        <v>0.05960778146982193</v>
       </c>
       <c r="H9" s="1"/>
       <c r="I9" t="s">
@@ -2286,22 +2286,22 @@
         <v>31890754</v>
       </c>
       <c r="B10" s="2">
-        <v>183692737.90720633</v>
+        <v>117469879.35538004</v>
       </c>
       <c r="C10" s="2">
-        <v>404023412785152</v>
+        <v>214568982806528</v>
       </c>
       <c r="D10" s="1">
-        <v>0.99301356077194214</v>
+        <v>0.9930146336555481</v>
       </c>
       <c r="E10" s="2">
-        <v>191792217.33230472</v>
+        <v>121147961.68756756</v>
       </c>
       <c r="F10" s="1">
-        <v>6724635</v>
+        <v>4394902.5</v>
       </c>
       <c r="G10" s="1">
-        <v>0.039642833173274994</v>
+        <v>0.0621340312063694</v>
       </c>
       <c r="H10" s="1"/>
       <c r="I10" t="s">
@@ -2313,22 +2313,22 @@
         <v>31890754</v>
       </c>
       <c r="B11" s="2">
-        <v>201714223.17612234</v>
+        <v>125056773.74346323</v>
       </c>
       <c r="C11" s="2">
-        <v>440147174752256</v>
+        <v>230454573662208</v>
       </c>
       <c r="D11" s="1">
-        <v>0.99402976036071777</v>
+        <v>0.99402981996536255</v>
       </c>
       <c r="E11" s="2">
-        <v>212330537.19577894</v>
+        <v>130992068.57227057</v>
       </c>
       <c r="F11" s="1">
-        <v>6724635</v>
+        <v>4394902.5</v>
       </c>
       <c r="G11" s="1">
-        <v>0.042176220566034317</v>
+        <v>0.067770332098007202</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" t="s">
@@ -2340,22 +2340,22 @@
         <v>31890754</v>
       </c>
       <c r="B12" s="2">
-        <v>225494497.77777779</v>
+        <v>140251030.5719921</v>
       </c>
       <c r="C12" s="2">
-        <v>486881116553216</v>
+        <v>250856138080256</v>
       </c>
       <c r="D12" s="1">
         <v>0.99504601955413818</v>
       </c>
       <c r="E12" s="2">
-        <v>239666529.57659552</v>
+        <v>145307686.37365383</v>
       </c>
       <c r="F12" s="1">
-        <v>6724635</v>
+        <v>4394902.5</v>
       </c>
       <c r="G12" s="1">
-        <v>0.04556858167052269</v>
+        <v>0.075485080480575562</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" t="s">
@@ -2367,22 +2367,22 @@
         <v>31890754</v>
       </c>
       <c r="B13" s="2">
-        <v>257703744.0828402</v>
+        <v>152266327.24580455</v>
       </c>
       <c r="C13" s="2">
-        <v>550670004387840</v>
+        <v>278093830815744</v>
       </c>
       <c r="D13" s="1">
-        <v>0.99606209993362427</v>
+        <v>0.99606215953826904</v>
       </c>
       <c r="E13" s="2">
-        <v>277076647.19433933</v>
+        <v>159448302.86673471</v>
       </c>
       <c r="F13" s="1">
-        <v>6724635</v>
+        <v>4394902.5</v>
       </c>
       <c r="G13" s="1">
-        <v>0.04819105938076973</v>
+        <v>0.083559408783912659</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" t="s">
@@ -2394,22 +2394,22 @@
         <v>31890754</v>
       </c>
       <c r="B14" s="2">
-        <v>301778241.97530866</v>
+        <v>172275376.60414612</v>
       </c>
       <c r="C14" s="2">
-        <v>637995648548864</v>
+        <v>315960644861952</v>
       </c>
       <c r="D14" s="1">
         <v>0.99701488018035889</v>
       </c>
       <c r="E14" s="2">
-        <v>333459955.01027531</v>
+        <v>183997264.46274185</v>
       </c>
       <c r="F14" s="1">
-        <v>6724635</v>
+        <v>4394902.5</v>
       </c>
       <c r="G14" s="1">
-        <v>0.051128000020980835</v>
+        <v>0.092322118580341339</v>
       </c>
       <c r="H14" s="1"/>
       <c r="I14" t="s">
@@ -2421,22 +2421,22 @@
         <v>31890754</v>
       </c>
       <c r="B15" s="2">
-        <v>378224505.67901236</v>
+        <v>195651063.20987654</v>
       </c>
       <c r="C15" s="2">
-        <v>795179103551488</v>
+        <v>384075571396608</v>
       </c>
       <c r="D15" s="1">
         <v>0.9980311393737793</v>
       </c>
       <c r="E15" s="2">
-        <v>446331024.39520228</v>
+        <v>219656803.38057619</v>
       </c>
       <c r="F15" s="1">
-        <v>6724635</v>
+        <v>4394902.5</v>
       </c>
       <c r="G15" s="1">
-        <v>0.051658809185028076</v>
+        <v>0.10505262762308121</v>
       </c>
       <c r="H15" s="1"/>
       <c r="I15" t="s">
@@ -2448,22 +2448,22 @@
         <v>31890754</v>
       </c>
       <c r="B16" s="2">
-        <v>562390452.34567904</v>
+        <v>294390394.07407409</v>
       </c>
       <c r="C16" s="2">
-        <v>1218789177819136</v>
+        <v>583725314211840</v>
       </c>
       <c r="D16" s="1">
         <v>0.99911081790924072</v>
       </c>
       <c r="E16" s="2">
-        <v>587676687.9032259</v>
+        <v>304125350.51020414</v>
       </c>
       <c r="F16" s="1">
-        <v>6724635</v>
+        <v>4394902.5</v>
       </c>
       <c r="G16" s="1">
-        <v>0.06114998459815979</v>
+        <v>0.11813382804393768</v>
       </c>
       <c r="H16" s="1"/>
       <c r="I16" t="s">
@@ -2475,22 +2475,22 @@
         <v>31890754</v>
       </c>
       <c r="B17" s="2">
-        <v>644534911.15498519</v>
+        <v>318147226.06120425</v>
       </c>
       <c r="C17" s="2">
-        <v>1390900328529920</v>
+        <v>659975210795008</v>
       </c>
       <c r="D17" s="1">
         <v>0.99930137395858765</v>
       </c>
       <c r="E17" s="2">
-        <v>662772035.05307329</v>
+        <v>320764201.9254505</v>
       </c>
       <c r="F17" s="1">
-        <v>6724635</v>
+        <v>4394902.5</v>
       </c>
       <c r="G17" s="1">
-        <v>0.058097310364246369</v>
+        <v>0.12000765651464462</v>
       </c>
       <c r="H17" s="1"/>
       <c r="I17" t="s">
@@ -2502,22 +2502,22 @@
         <v>31890754</v>
       </c>
       <c r="B18" s="2">
-        <v>722960038.00592303</v>
+        <v>356646403.25765056</v>
       </c>
       <c r="C18" s="2">
-        <v>1552711208140800</v>
+        <v>735357591093248</v>
       </c>
       <c r="D18" s="1">
         <v>0.999428391456604</v>
       </c>
       <c r="E18" s="2">
-        <v>777802300.31265426</v>
+        <v>374090978.11420107</v>
       </c>
       <c r="F18" s="1">
-        <v>6724635</v>
+        <v>4394902.5</v>
       </c>
       <c r="G18" s="1">
-        <v>0.058944627642631531</v>
+        <v>0.12250236421823502</v>
       </c>
       <c r="H18" s="1"/>
       <c r="I18" t="s">
@@ -2529,22 +2529,22 @@
         <v>31890754</v>
       </c>
       <c r="B19" s="2">
-        <v>910814742.22222221</v>
+        <v>426393169.382716</v>
       </c>
       <c r="C19" s="2">
-        <v>1940229330042880</v>
+        <v>916020558561280</v>
       </c>
       <c r="D19" s="1">
         <v>0.99961894750595093</v>
       </c>
       <c r="E19" s="2">
-        <v>1027657585.4180383</v>
+        <v>481791479.42725474</v>
       </c>
       <c r="F19" s="1">
-        <v>6724635</v>
+        <v>4394902.5</v>
       </c>
       <c r="G19" s="1">
-        <v>0.057281993329524994</v>
+        <v>0.12223166227340698</v>
       </c>
       <c r="H19" s="1"/>
       <c r="I19" t="s">
@@ -2556,22 +2556,22 @@
         <v>31890754</v>
       </c>
       <c r="B20" s="2">
-        <v>1403260381.5399802</v>
+        <v>644670794.17571545</v>
       </c>
       <c r="C20" s="2">
-        <v>2852801029865472</v>
+        <v>1350249536815104</v>
       </c>
       <c r="D20" s="1">
         <v>0.99980950355529785</v>
       </c>
       <c r="E20" s="2">
-        <v>2852801033.4101386</v>
+        <v>1350249692.0671492</v>
       </c>
       <c r="F20" s="1">
-        <v>6724635</v>
+        <v>4394902.5</v>
       </c>
       <c r="G20" s="1">
-        <v>0.051203593611717224</v>
+        <v>0.10975739359855652</v>
       </c>
       <c r="H20" s="1"/>
       <c r="I20" t="s">
@@ -2621,22 +2621,22 @@
         <v>32705576</v>
       </c>
       <c r="B2" s="2">
-        <v>9623114.0144073348</v>
+        <v>8553565.2259332035</v>
       </c>
       <c r="C2" s="2">
-        <v>132431004827648</v>
+        <v>69982008377344</v>
       </c>
       <c r="D2" s="1">
         <v>0.91001802682876587</v>
       </c>
       <c r="E2" s="2">
-        <v>20675104.996987924</v>
+        <v>18369557.462023795</v>
       </c>
       <c r="F2" s="1">
-        <v>11927713</v>
+        <v>6306717.5</v>
       </c>
       <c r="G2" s="1">
-        <v>0.0032582688145339489</v>
+        <v>0.0036774363834410906</v>
       </c>
       <c r="H2" s="1">
         <v>2017</v>
@@ -2650,22 +2650,22 @@
         <v>32705576</v>
       </c>
       <c r="B3" s="2">
-        <v>30552356.769130152</v>
+        <v>26237962.418300655</v>
       </c>
       <c r="C3" s="2">
-        <v>146417783930880</v>
+        <v>76478981079040</v>
       </c>
       <c r="D3" s="1">
-        <v>0.92002701759338379</v>
+        <v>0.92007851600646973</v>
       </c>
       <c r="E3" s="2">
-        <v>38724388.669288911</v>
+        <v>33166905.934954926</v>
       </c>
       <c r="F3" s="1">
-        <v>11927713</v>
+        <v>6306717.5</v>
       </c>
       <c r="G3" s="1">
-        <v>0.0034145996905863285</v>
+        <v>0.004024554044008255</v>
       </c>
       <c r="H3" s="1"/>
       <c r="I3" t="s">
@@ -2677,22 +2677,22 @@
         <v>32705576</v>
       </c>
       <c r="B4" s="2">
-        <v>45471639.063015506</v>
+        <v>39097381.557510592</v>
       </c>
       <c r="C4" s="2">
-        <v>161823143755776</v>
+        <v>82710550806528</v>
       </c>
       <c r="D4" s="1">
-        <v>0.93003535270690918</v>
+        <v>0.93013101816177368</v>
       </c>
       <c r="E4" s="2">
-        <v>49464749.194803186</v>
+        <v>43643654.855491027</v>
       </c>
       <c r="F4" s="1">
-        <v>11927713</v>
+        <v>6306717.5</v>
       </c>
       <c r="G4" s="1">
-        <v>0.0024333817418664694</v>
+        <v>0.0028881654143333435</v>
       </c>
       <c r="H4" s="1"/>
       <c r="I4" t="s">
@@ -2704,22 +2704,22 @@
         <v>32705576</v>
       </c>
       <c r="B5" s="2">
-        <v>53528123.610202745</v>
+        <v>47605894.271685764</v>
       </c>
       <c r="C5" s="2">
-        <v>180577890205696</v>
+        <v>89176171085824</v>
       </c>
       <c r="D5" s="1">
-        <v>0.94004327058792114</v>
+        <v>0.94005239009857178</v>
       </c>
       <c r="E5" s="2">
-        <v>57914513.805091016</v>
+        <v>50325416.327607669</v>
       </c>
       <c r="F5" s="1">
-        <v>11927713</v>
+        <v>6306717.5</v>
       </c>
       <c r="G5" s="1">
-        <v>0.0039467271417379379</v>
+        <v>0.0045690569095313549</v>
       </c>
       <c r="H5" s="1"/>
       <c r="I5" t="s">
@@ -2731,22 +2731,22 @@
         <v>32705576</v>
       </c>
       <c r="B6" s="2">
-        <v>62826424.272162251</v>
+        <v>53536420.864478387</v>
       </c>
       <c r="C6" s="2">
-        <v>205155807002624</v>
+        <v>96969724788736</v>
       </c>
       <c r="D6" s="1">
-        <v>0.95005136728286743</v>
+        <v>0.95006871223449707</v>
       </c>
       <c r="E6" s="2">
-        <v>68783938.346856043</v>
+        <v>57343059.512520738</v>
       </c>
       <c r="F6" s="1">
-        <v>11927713</v>
+        <v>6306717.5</v>
       </c>
       <c r="G6" s="1">
-        <v>0.0086646173149347305</v>
+        <v>0.010577918961644173</v>
       </c>
       <c r="H6" s="1"/>
       <c r="I6" t="s">
@@ -2758,22 +2758,22 @@
         <v>32705576</v>
       </c>
       <c r="B7" s="2">
-        <v>75593294.959349588</v>
+        <v>61197363.319010429</v>
       </c>
       <c r="C7" s="2">
-        <v>239327908986880</v>
+        <v>106907155038208</v>
       </c>
       <c r="D7" s="1">
-        <v>0.96005964279174805</v>
+        <v>0.96007978916168213</v>
       </c>
       <c r="E7" s="2">
-        <v>83988723.7411374</v>
+        <v>65871980.594863385</v>
       </c>
       <c r="F7" s="1">
-        <v>11927713</v>
+        <v>6306717.5</v>
       </c>
       <c r="G7" s="1">
-        <v>0.014370170421898365</v>
+        <v>0.018649930134415627</v>
       </c>
       <c r="H7" s="1"/>
       <c r="I7" t="s">
@@ -2785,22 +2785,22 @@
         <v>32705576</v>
       </c>
       <c r="B8" s="2">
-        <v>93710357.391579613</v>
+        <v>69445458.005880415</v>
       </c>
       <c r="C8" s="2">
-        <v>291251261800448</v>
+        <v>120631093886976</v>
       </c>
       <c r="D8" s="1">
-        <v>0.97006547451019287</v>
+        <v>0.97008472681045532</v>
       </c>
       <c r="E8" s="2">
-        <v>106887326.0248695</v>
+        <v>76348222.208785966</v>
       </c>
       <c r="F8" s="1">
-        <v>11927713</v>
+        <v>6306717.5</v>
       </c>
       <c r="G8" s="1">
-        <v>0.020542195066809654</v>
+        <v>0.028371803462505341</v>
       </c>
       <c r="H8" s="1"/>
       <c r="I8" t="s">
@@ -2812,22 +2812,22 @@
         <v>32705576</v>
       </c>
       <c r="B9" s="2">
-        <v>123578003.92156863</v>
+        <v>89844575.351422012</v>
       </c>
       <c r="C9" s="2">
-        <v>383894713008128</v>
+        <v>142840009064448</v>
       </c>
       <c r="D9" s="1">
-        <v>0.98007690906524658</v>
+        <v>0.98007673025131226</v>
       </c>
       <c r="E9" s="2">
-        <v>154674546.24799973</v>
+        <v>103323761.56048389</v>
       </c>
       <c r="F9" s="1">
-        <v>11927713</v>
+        <v>6306717.5</v>
       </c>
       <c r="G9" s="1">
-        <v>0.033436398953199387</v>
+        <v>0.050027895718812943</v>
       </c>
       <c r="H9" s="1"/>
       <c r="I9" t="s">
@@ -2839,22 +2839,22 @@
         <v>32705576</v>
       </c>
       <c r="B10" s="2">
-        <v>202182207.71998692</v>
+        <v>118094513.08044475</v>
       </c>
       <c r="C10" s="2">
-        <v>615276546621440</v>
+        <v>182730138583040</v>
       </c>
       <c r="D10" s="1">
-        <v>0.9900851845741272</v>
+        <v>0.99008524417877197</v>
       </c>
       <c r="E10" s="2">
-        <v>208666232.31458175</v>
+        <v>120311211.57165273</v>
       </c>
       <c r="F10" s="1">
-        <v>11927713</v>
+        <v>6306717.5</v>
       </c>
       <c r="G10" s="1">
-        <v>0.03779330849647522</v>
+        <v>0.065155401825904846</v>
       </c>
       <c r="H10" s="1"/>
       <c r="I10" t="s">
@@ -2866,22 +2866,22 @@
         <v>32705576</v>
       </c>
       <c r="B11" s="2">
-        <v>217054388.1621975</v>
+        <v>123680076.8476128</v>
       </c>
       <c r="C11" s="2">
-        <v>657634252292096</v>
+        <v>189232282861568</v>
       </c>
       <c r="D11" s="1">
         <v>0.99102061986923218</v>
       </c>
       <c r="E11" s="2">
-        <v>225762039.54872358</v>
+        <v>127789311.45000149</v>
       </c>
       <c r="F11" s="1">
-        <v>11927713</v>
+        <v>6306717.5</v>
       </c>
       <c r="G11" s="1">
-        <v>0.039407268166542053</v>
+        <v>0.070250995457172394</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" t="s">
@@ -2893,22 +2893,22 @@
         <v>32705576</v>
       </c>
       <c r="B12" s="2">
-        <v>236934604.90196079</v>
+        <v>130953795.94506213</v>
       </c>
       <c r="C12" s="2">
-        <v>713520970727424</v>
+        <v>197178593116160</v>
       </c>
       <c r="D12" s="1">
-        <v>0.9920494556427002</v>
+        <v>0.99204891920089722</v>
       </c>
       <c r="E12" s="2">
-        <v>247655832.72910973</v>
+        <v>133621016.81421189</v>
       </c>
       <c r="F12" s="1">
-        <v>11927713</v>
+        <v>6306717.5</v>
       </c>
       <c r="G12" s="1">
-        <v>0.040424082428216934</v>
+        <v>0.074671193957328796</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" t="s">
@@ -2920,22 +2920,22 @@
         <v>32705576</v>
       </c>
       <c r="B13" s="2">
-        <v>261645447.8587774</v>
+        <v>137992946.52755138</v>
       </c>
       <c r="C13" s="2">
-        <v>782774634020864</v>
+        <v>206629333106688</v>
       </c>
       <c r="D13" s="1">
-        <v>0.99307841062545776</v>
+        <v>0.99307817220687866</v>
       </c>
       <c r="E13" s="2">
-        <v>274045059.69466144</v>
+        <v>141189402.14407116</v>
       </c>
       <c r="F13" s="1">
-        <v>11927713</v>
+        <v>6306717.5</v>
       </c>
       <c r="G13" s="1">
-        <v>0.042026635259389877</v>
+        <v>0.081234514713287354</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" t="s">
@@ -2947,22 +2947,22 @@
         <v>32705576</v>
       </c>
       <c r="B14" s="2">
-        <v>290395338.35571569</v>
+        <v>145461528.77697846</v>
       </c>
       <c r="C14" s="2">
-        <v>862256963256320</v>
+        <v>216855801233408</v>
       </c>
       <c r="D14" s="1">
         <v>0.99401366710662842</v>
       </c>
       <c r="E14" s="2">
-        <v>308144540.23535007</v>
+        <v>147902740.05824494</v>
       </c>
       <c r="F14" s="1">
-        <v>11927713</v>
+        <v>6306717.5</v>
       </c>
       <c r="G14" s="1">
-        <v>0.042234234511852264</v>
+        <v>0.088612668216228485</v>
       </c>
       <c r="H14" s="1"/>
       <c r="I14" t="s">
@@ -2974,22 +2974,22 @@
         <v>32705576</v>
       </c>
       <c r="B15" s="2">
-        <v>331764693.03694016</v>
+        <v>157443702.9411765</v>
       </c>
       <c r="C15" s="2">
-        <v>977266657984512</v>
+        <v>231166967808000</v>
       </c>
       <c r="D15" s="1">
-        <v>0.99504262208938599</v>
+        <v>0.99504256248474121</v>
       </c>
       <c r="E15" s="2">
-        <v>356029982.79355127</v>
+        <v>160199304.5971888</v>
       </c>
       <c r="F15" s="1">
-        <v>11927713</v>
+        <v>6306717.5</v>
       </c>
       <c r="G15" s="1">
-        <v>0.043706510215997696</v>
+        <v>0.09630228579044342</v>
       </c>
       <c r="H15" s="1"/>
       <c r="I15" t="s">
@@ -3001,22 +3001,22 @@
         <v>32705576</v>
       </c>
       <c r="B16" s="2">
-        <v>389130627.45098037</v>
+        <v>163575651.96078435</v>
       </c>
       <c r="C16" s="2">
-        <v>1139968743309312</v>
+        <v>249753975652352</v>
       </c>
       <c r="D16" s="1">
         <v>0.99607151746749878</v>
       </c>
       <c r="E16" s="2">
-        <v>420765390.63776928</v>
+        <v>167965426.07795906</v>
       </c>
       <c r="F16" s="1">
-        <v>11927713</v>
+        <v>6306717.5</v>
       </c>
       <c r="G16" s="1">
-        <v>0.040532369166612625</v>
+        <v>0.099340595304965973</v>
       </c>
       <c r="H16" s="1"/>
       <c r="I16" t="s">
@@ -3028,22 +3028,22 @@
         <v>32705576</v>
       </c>
       <c r="B17" s="2">
-        <v>466147931.69934642</v>
+        <v>172929877.45098034</v>
       </c>
       <c r="C17" s="2">
-        <v>1364715791974400</v>
+        <v>275314584322048</v>
       </c>
       <c r="D17" s="1">
-        <v>0.99700683355331421</v>
+        <v>0.99700689315795899</v>
       </c>
       <c r="E17" s="2">
-        <v>524350237.32319027</v>
+        <v>187123278.54383361</v>
       </c>
       <c r="F17" s="1">
-        <v>11927713</v>
+        <v>6306717.5</v>
       </c>
       <c r="G17" s="1">
-        <v>0.038654502481222153</v>
+        <v>0.11033853143453598</v>
       </c>
       <c r="H17" s="1"/>
       <c r="I17" t="s">
@@ -3055,22 +3055,22 @@
         <v>32705576</v>
       </c>
       <c r="B18" s="2">
-        <v>622912483.81824124</v>
+        <v>205519666.55769864</v>
       </c>
       <c r="C18" s="2">
-        <v>1804932759945216</v>
+        <v>321509977489408</v>
       </c>
       <c r="D18" s="1">
         <v>0.99803578853607178</v>
       </c>
       <c r="E18" s="2">
-        <v>781615812.03566122</v>
+        <v>222161015.8989599</v>
       </c>
       <c r="F18" s="1">
-        <v>11927713</v>
+        <v>6306717.5</v>
       </c>
       <c r="G18" s="1">
-        <v>0.037064094096422195</v>
+        <v>0.12860654294490814</v>
       </c>
       <c r="H18" s="1"/>
       <c r="I18" t="s">
@@ -3082,22 +3082,22 @@
         <v>32705576</v>
       </c>
       <c r="B19" s="2">
-        <v>1080186810.0686498</v>
+        <v>252598881.00686491</v>
       </c>
       <c r="C19" s="2">
-        <v>2930577787322368</v>
+        <v>430793541287936</v>
       </c>
       <c r="D19" s="1">
         <v>0.99906468391418457</v>
       </c>
       <c r="E19" s="2">
-        <v>1126921739.7842431</v>
+        <v>257493982.34717217</v>
       </c>
       <c r="F19" s="1">
-        <v>11927713</v>
+        <v>6306717.5</v>
       </c>
       <c r="G19" s="1">
-        <v>0.031134206801652908</v>
+        <v>0.13584557175636292</v>
       </c>
       <c r="H19" s="1"/>
       <c r="I19" t="s">
@@ -3109,22 +3109,22 @@
         <v>32705576</v>
       </c>
       <c r="B20" s="2">
-        <v>1287585430.7189543</v>
+        <v>272999450.65359479</v>
       </c>
       <c r="C20" s="2">
-        <v>3381473654603776</v>
+        <v>474116675076096</v>
       </c>
       <c r="D20" s="1">
         <v>0.99925172328948975</v>
       </c>
       <c r="E20" s="2">
-        <v>1358563009.6420984</v>
+        <v>284590195.94705021</v>
       </c>
       <c r="F20" s="1">
-        <v>11927713</v>
+        <v>6306717.5</v>
       </c>
       <c r="G20" s="1">
-        <v>0.028657224029302597</v>
+        <v>0.13664136826992035</v>
       </c>
       <c r="H20" s="1"/>
       <c r="I20" t="s">
@@ -3136,22 +3136,22 @@
         <v>32705576</v>
       </c>
       <c r="B21" s="2">
-        <v>1614981805.1650867</v>
+        <v>305240753.84112448</v>
       </c>
       <c r="C21" s="2">
-        <v>4055887404597248</v>
+        <v>537302455549952</v>
       </c>
       <c r="D21" s="1">
         <v>0.9994388222694397</v>
       </c>
       <c r="E21" s="2">
-        <v>1741526298.136646</v>
+        <v>323955735.37103635</v>
       </c>
       <c r="F21" s="1">
-        <v>11927713</v>
+        <v>6306717.5</v>
       </c>
       <c r="G21" s="1">
-        <v>0.026543557643890381</v>
+        <v>0.14248120784759522</v>
       </c>
       <c r="H21" s="1"/>
       <c r="I21" t="s">
@@ -3163,22 +3163,22 @@
         <v>32705576</v>
       </c>
       <c r="B22" s="2">
-        <v>2218041796.0117683</v>
+        <v>372961863.35403717</v>
       </c>
       <c r="C22" s="2">
-        <v>5213067558256640</v>
+        <v>643975853637632</v>
       </c>
       <c r="D22" s="1">
         <v>0.99962586164474487</v>
       </c>
       <c r="E22" s="2">
-        <v>2505214453.5796008</v>
+        <v>385000086.13926131</v>
       </c>
       <c r="F22" s="1">
-        <v>11927713</v>
+        <v>6306717.5</v>
       </c>
       <c r="G22" s="1">
-        <v>0.022368401288986206</v>
+        <v>0.14429870247840881</v>
       </c>
       <c r="H22" s="1"/>
       <c r="I22" t="s">
@@ -3190,22 +3190,22 @@
         <v>32705576</v>
       </c>
       <c r="B23" s="2">
-        <v>3951656334.0961099</v>
+        <v>524038264.79241592</v>
       </c>
       <c r="C23" s="2">
-        <v>7920921494945792</v>
+        <v>902951644168192</v>
       </c>
       <c r="D23" s="1">
         <v>0.99981296062469482</v>
       </c>
       <c r="E23" s="2">
-        <v>7920921418.2739458</v>
+        <v>902951617.68551815</v>
       </c>
       <c r="F23" s="1">
-        <v>11927713</v>
+        <v>6306717.5</v>
       </c>
       <c r="G23" s="1">
-        <v>0.016396239399909973</v>
+        <v>0.13620215654373169</v>
       </c>
       <c r="H23" s="1"/>
       <c r="I23" t="s">
@@ -3255,22 +3255,22 @@
         <v>33679876</v>
       </c>
       <c r="B2" s="2">
-        <v>18913341.551849168</v>
+        <v>17285494.198694706</v>
       </c>
       <c r="C2" s="2">
-        <v>138341215371264</v>
+        <v>74535156056064</v>
       </c>
       <c r="D2" s="1">
         <v>0.91003322601318359</v>
       </c>
       <c r="E2" s="2">
-        <v>27671593.772538137</v>
+        <v>24178580.274566039</v>
       </c>
       <c r="F2" s="1">
-        <v>12514700</v>
+        <v>6767786.5</v>
       </c>
       <c r="G2" s="1">
-        <v>0.0029136913362890482</v>
+        <v>0.0033465384040027857</v>
       </c>
       <c r="H2" s="1">
         <v>2018</v>
@@ -3284,22 +3284,22 @@
         <v>33679876</v>
       </c>
       <c r="B3" s="2">
-        <v>36404095.686512761</v>
+        <v>31222477.452772699</v>
       </c>
       <c r="C3" s="2">
-        <v>152276471644160</v>
+        <v>80875777687552</v>
       </c>
       <c r="D3" s="1">
-        <v>0.92009472846984863</v>
+        <v>0.92009449005126953</v>
       </c>
       <c r="E3" s="2">
-        <v>43265954.00421387</v>
+        <v>37127008.975999296</v>
       </c>
       <c r="F3" s="1">
-        <v>12514700</v>
+        <v>6767786.5</v>
       </c>
       <c r="G3" s="1">
-        <v>0.0026813417207449675</v>
+        <v>0.0031482367776334286</v>
       </c>
       <c r="H3" s="1"/>
       <c r="I3" t="s">
@@ -3311,22 +3311,22 @@
         <v>33679876</v>
       </c>
       <c r="B4" s="2">
-        <v>48615033.816425122</v>
+        <v>42357170.163934432</v>
       </c>
       <c r="C4" s="2">
-        <v>167804942680064</v>
+        <v>87135457640448</v>
       </c>
       <c r="D4" s="1">
-        <v>0.93005788326263428</v>
+        <v>0.93009644746780396</v>
       </c>
       <c r="E4" s="2">
-        <v>52721789.573574908</v>
+        <v>46334634.008051485</v>
       </c>
       <c r="F4" s="1">
-        <v>12514700</v>
+        <v>6767786.5</v>
       </c>
       <c r="G4" s="1">
-        <v>0.0022543005179613829</v>
+        <v>0.0026062186807394028</v>
       </c>
       <c r="H4" s="1"/>
       <c r="I4" t="s">
@@ -3338,22 +3338,22 @@
         <v>33679876</v>
       </c>
       <c r="B5" s="2">
-        <v>57080353.958143771</v>
+        <v>49967122.887864821</v>
       </c>
       <c r="C5" s="2">
-        <v>186923654053888</v>
+        <v>93923879944192</v>
       </c>
       <c r="D5" s="1">
-        <v>0.94002199172973633</v>
+        <v>0.94006794691085815</v>
       </c>
       <c r="E5" s="2">
-        <v>61642366.019128099</v>
+        <v>53042290.911044821</v>
       </c>
       <c r="F5" s="1">
-        <v>12514700</v>
+        <v>6767786.5</v>
       </c>
       <c r="G5" s="1">
-        <v>0.0037480802275240421</v>
+        <v>0.0045802216045558453</v>
       </c>
       <c r="H5" s="1"/>
       <c r="I5" t="s">
@@ -3365,22 +3365,22 @@
         <v>33679876</v>
       </c>
       <c r="B6" s="2">
-        <v>66772966.106870227</v>
+        <v>56398806.361412093</v>
       </c>
       <c r="C6" s="2">
-        <v>212176434364416</v>
+        <v>102058564780032</v>
       </c>
       <c r="D6" s="1">
-        <v>0.95008361339569092</v>
+        <v>0.95001417398452759</v>
       </c>
       <c r="E6" s="2">
-        <v>72996337.893076599</v>
+        <v>60678052.416718692</v>
       </c>
       <c r="F6" s="1">
-        <v>12514700</v>
+        <v>6767786.5</v>
       </c>
       <c r="G6" s="1">
-        <v>0.0085312416777014732</v>
+        <v>0.01007495354861021</v>
       </c>
       <c r="H6" s="1"/>
       <c r="I6" t="s">
@@ -3392,22 +3392,22 @@
         <v>33679876</v>
       </c>
       <c r="B7" s="2">
-        <v>80052624.457935825</v>
+        <v>64833724.765080318</v>
       </c>
       <c r="C7" s="2">
-        <v>246863311667200</v>
+        <v>112455128711168</v>
       </c>
       <c r="D7" s="1">
-        <v>0.96004205942153931</v>
+        <v>0.96005105972290039</v>
       </c>
       <c r="E7" s="2">
-        <v>88673930.288557485</v>
+        <v>69387004.512833864</v>
       </c>
       <c r="F7" s="1">
-        <v>12514700</v>
+        <v>6767786.5</v>
       </c>
       <c r="G7" s="1">
-        <v>0.013975675217807293</v>
+        <v>0.018323633819818497</v>
       </c>
       <c r="H7" s="1"/>
       <c r="I7" t="s">
@@ -3419,22 +3419,22 @@
         <v>33679876</v>
       </c>
       <c r="B8" s="2">
-        <v>98471158.754157841</v>
+        <v>73783442.348646179</v>
       </c>
       <c r="C8" s="2">
-        <v>299445723856896</v>
+        <v>126789397512192</v>
       </c>
       <c r="D8" s="1">
-        <v>0.97001057863235474</v>
+        <v>0.97002691030502319</v>
       </c>
       <c r="E8" s="2">
-        <v>112304730.08463959</v>
+        <v>81280920.32399936</v>
       </c>
       <c r="F8" s="1">
-        <v>12514700</v>
+        <v>6767786.5</v>
       </c>
       <c r="G8" s="1">
-        <v>0.020206118002533913</v>
+        <v>0.027484238147735596</v>
       </c>
       <c r="H8" s="1"/>
       <c r="I8" t="s">
@@ -3446,22 +3446,22 @@
         <v>33679876</v>
       </c>
       <c r="B9" s="2">
-        <v>129892687.0252203</v>
+        <v>94479201.336167634</v>
       </c>
       <c r="C9" s="2">
-        <v>393938057822208</v>
+        <v>149730545893376</v>
       </c>
       <c r="D9" s="1">
         <v>0.9800724983215332</v>
       </c>
       <c r="E9" s="2">
-        <v>161837345.17161438</v>
+        <v>108488263.13107534</v>
       </c>
       <c r="F9" s="1">
-        <v>12514700</v>
+        <v>6767786.5</v>
       </c>
       <c r="G9" s="1">
-        <v>0.033101502805948257</v>
+        <v>0.049498055130243301</v>
       </c>
       <c r="H9" s="1"/>
       <c r="I9" t="s">
@@ -3473,22 +3473,22 @@
         <v>33679876</v>
       </c>
       <c r="B10" s="2">
-        <v>209874072.31844425</v>
+        <v>125600577.20364745</v>
       </c>
       <c r="C10" s="2">
-        <v>626038795141120</v>
+        <v>190972952576000</v>
       </c>
       <c r="D10" s="1">
         <v>0.9900362491607666</v>
       </c>
       <c r="E10" s="2">
-        <v>216776104.95121732</v>
+        <v>127905798.48001213</v>
       </c>
       <c r="F10" s="1">
-        <v>12514700</v>
+        <v>6767786.5</v>
       </c>
       <c r="G10" s="1">
-        <v>0.038717333227396011</v>
+        <v>0.065600551664829254</v>
       </c>
       <c r="H10" s="1"/>
       <c r="I10" t="s">
@@ -3500,22 +3500,22 @@
         <v>33679876</v>
       </c>
       <c r="B11" s="2">
-        <v>225820726.96868348</v>
+        <v>129900382.37082067</v>
       </c>
       <c r="C11" s="2">
-        <v>670525663739904</v>
+        <v>197826998960128</v>
       </c>
       <c r="D11" s="1">
-        <v>0.99101310968399048</v>
+        <v>0.99101299047470093</v>
       </c>
       <c r="E11" s="2">
-        <v>235130910.93732733</v>
+        <v>132612478.39301501</v>
       </c>
       <c r="F11" s="1">
-        <v>12514700</v>
+        <v>6767786.5</v>
       </c>
       <c r="G11" s="1">
-        <v>0.039123449474573135</v>
+        <v>0.06873522698879242</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" t="s">
@@ -3527,22 +3527,22 @@
         <v>33679876</v>
       </c>
       <c r="B12" s="2">
-        <v>247150009.11300123</v>
+        <v>137673195.92952609</v>
       </c>
       <c r="C12" s="2">
-        <v>729650250645504</v>
+        <v>206683775172608</v>
       </c>
       <c r="D12" s="1">
-        <v>0.99208760261535645</v>
+        <v>0.99208754301071167</v>
       </c>
       <c r="E12" s="2">
-        <v>257585759.13014409</v>
+        <v>140731642.93659961</v>
       </c>
       <c r="F12" s="1">
-        <v>12514700</v>
+        <v>6767786.5</v>
       </c>
       <c r="G12" s="1">
-        <v>0.039926078170537949</v>
+        <v>0.07406347244977951</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" t="s">
@@ -3554,22 +3554,22 @@
         <v>33679876</v>
       </c>
       <c r="B13" s="2">
-        <v>271256338.09668595</v>
+        <v>144297828.51930678</v>
       </c>
       <c r="C13" s="2">
-        <v>796143122382848</v>
+        <v>215973453889536</v>
       </c>
       <c r="D13" s="1">
-        <v>0.9930645227432251</v>
+        <v>0.99306446313858032</v>
       </c>
       <c r="E13" s="2">
-        <v>284474803.61105204</v>
+        <v>147200099.94832355</v>
       </c>
       <c r="F13" s="1">
-        <v>12514700</v>
+        <v>6767786.5</v>
       </c>
       <c r="G13" s="1">
-        <v>0.041392028331756592</v>
+        <v>0.079091034829616547</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" t="s">
@@ -3581,22 +3581,22 @@
         <v>33679876</v>
       </c>
       <c r="B14" s="2">
-        <v>301759051.38339919</v>
+        <v>151279927.22576723</v>
       </c>
       <c r="C14" s="2">
-        <v>880021417754624</v>
+        <v>227246686076928</v>
       </c>
       <c r="D14" s="1">
-        <v>0.9940413236618042</v>
+        <v>0.99404120445251465</v>
       </c>
       <c r="E14" s="2">
-        <v>318838852.32073933</v>
+        <v>154801218.19535616</v>
       </c>
       <c r="F14" s="1">
-        <v>12514700</v>
+        <v>6767786.5</v>
       </c>
       <c r="G14" s="1">
-        <v>0.042277481406927109</v>
+        <v>0.088265053927898407</v>
       </c>
       <c r="H14" s="1"/>
       <c r="I14" t="s">
@@ -3608,22 +3608,22 @@
         <v>33679876</v>
       </c>
       <c r="B15" s="2">
-        <v>341946739.89668793</v>
+        <v>162907330.59610704</v>
       </c>
       <c r="C15" s="2">
-        <v>990054520455168</v>
+        <v>241453666140160</v>
       </c>
       <c r="D15" s="1">
-        <v>0.9950181245803833</v>
+        <v>0.99501818418502808</v>
       </c>
       <c r="E15" s="2">
-        <v>367214381.03395867</v>
+        <v>167542737.57219043</v>
       </c>
       <c r="F15" s="1">
-        <v>12514700</v>
+        <v>6767786.5</v>
       </c>
       <c r="G15" s="1">
-        <v>0.044154331088066101</v>
+        <v>0.094800248742103577</v>
       </c>
       <c r="H15" s="1"/>
       <c r="I15" t="s">
@@ -3635,22 +3635,22 @@
         <v>33679876</v>
       </c>
       <c r="B16" s="2">
-        <v>402241244.45120096</v>
+        <v>172748347.41641337</v>
       </c>
       <c r="C16" s="2">
-        <v>1161342916493312</v>
+        <v>261778911002624</v>
       </c>
       <c r="D16" s="1">
         <v>0.99609267711639404</v>
       </c>
       <c r="E16" s="2">
-        <v>437459623.16858161</v>
+        <v>177626262.18844986</v>
       </c>
       <c r="F16" s="1">
-        <v>12514700</v>
+        <v>6767786.5</v>
       </c>
       <c r="G16" s="1">
-        <v>0.04130597785115242</v>
+        <v>0.099533632397651672</v>
       </c>
       <c r="H16" s="1"/>
       <c r="I16" t="s">
@@ -3662,22 +3662,22 @@
         <v>33679876</v>
       </c>
       <c r="B17" s="2">
-        <v>485967868.1251899</v>
+        <v>184944556.70416537</v>
       </c>
       <c r="C17" s="2">
-        <v>1402622770675712</v>
+        <v>289830365822976</v>
       </c>
       <c r="D17" s="1">
-        <v>0.99706947803497315</v>
+        <v>0.99706953763961792</v>
       </c>
       <c r="E17" s="2">
-        <v>545180703.34346509</v>
+        <v>201107455.68119639</v>
       </c>
       <c r="F17" s="1">
-        <v>12514700</v>
+        <v>6767786.5</v>
       </c>
       <c r="G17" s="1">
-        <v>0.039956048130989075</v>
+        <v>0.11098692566156387</v>
       </c>
       <c r="H17" s="1"/>
       <c r="I17" t="s">
@@ -3689,22 +3689,22 @@
         <v>33679876</v>
       </c>
       <c r="B18" s="2">
-        <v>644280896.80948043</v>
+        <v>215406682.89273781</v>
       </c>
       <c r="C18" s="2">
-        <v>1831343721807872</v>
+        <v>334189123600384</v>
       </c>
       <c r="D18" s="1">
         <v>0.99804633855819702</v>
       </c>
       <c r="E18" s="2">
-        <v>793872015.17886984</v>
+        <v>235546392.76617733</v>
       </c>
       <c r="F18" s="1">
-        <v>12514700</v>
+        <v>6767786.5</v>
       </c>
       <c r="G18" s="1">
-        <v>0.038432631641626358</v>
+        <v>0.12847501039505005</v>
       </c>
       <c r="H18" s="1"/>
       <c r="I18" t="s">
@@ -3716,22 +3716,22 @@
         <v>33679876</v>
       </c>
       <c r="B19" s="2">
-        <v>1069230897.2644378</v>
+        <v>268548704.25531918</v>
       </c>
       <c r="C19" s="2">
-        <v>2868878434631680</v>
+        <v>432837845057536</v>
       </c>
       <c r="D19" s="1">
         <v>0.9990231990814209</v>
       </c>
       <c r="E19" s="2">
-        <v>1115303759.4224925</v>
+        <v>278183958.05471122</v>
       </c>
       <c r="F19" s="1">
-        <v>12514700</v>
+        <v>6767786.5</v>
       </c>
       <c r="G19" s="1">
-        <v>0.035265639424324036</v>
+        <v>0.14135423302650452</v>
       </c>
       <c r="H19" s="1"/>
       <c r="I19" t="s">
@@ -3743,22 +3743,22 @@
         <v>33679876</v>
       </c>
       <c r="B20" s="2">
-        <v>1272338507.294833</v>
+        <v>295064589.0577507</v>
       </c>
       <c r="C20" s="2">
-        <v>3307288831983616</v>
+        <v>471502818377728</v>
       </c>
       <c r="D20" s="1">
         <v>0.99921858310699463</v>
       </c>
       <c r="E20" s="2">
-        <v>1341737581.6109421</v>
+        <v>297995475.22796357</v>
       </c>
       <c r="F20" s="1">
-        <v>12514700</v>
+        <v>6767786.5</v>
       </c>
       <c r="G20" s="1">
-        <v>0.031175140291452408</v>
+        <v>0.14022554457187653</v>
       </c>
       <c r="H20" s="1"/>
       <c r="I20" t="s">
@@ -3770,22 +3770,22 @@
         <v>33679876</v>
       </c>
       <c r="B21" s="2">
-        <v>1591239464.43769</v>
+        <v>315430603.34346521</v>
       </c>
       <c r="C21" s="2">
-        <v>3962505688776704</v>
+        <v>529341532340224</v>
       </c>
       <c r="D21" s="1">
         <v>0.99941390752792358</v>
       </c>
       <c r="E21" s="2">
-        <v>1713608558.2066872</v>
+        <v>326800913.8297872</v>
       </c>
       <c r="F21" s="1">
-        <v>12514700</v>
+        <v>6767786.5</v>
       </c>
       <c r="G21" s="1">
-        <v>0.027668766677379608</v>
+        <v>0.14468815922737122</v>
       </c>
       <c r="H21" s="1"/>
       <c r="I21" t="s">
@@ -3797,22 +3797,22 @@
         <v>33679876</v>
       </c>
       <c r="B22" s="2">
-        <v>2184661439.8176293</v>
+        <v>391036194.52887523</v>
       </c>
       <c r="C22" s="2">
-        <v>5087039796019200</v>
+        <v>630619511980032</v>
       </c>
       <c r="D22" s="1">
         <v>0.99960929155349732</v>
       </c>
       <c r="E22" s="2">
-        <v>2467616110.1823711</v>
+        <v>395787025.98784191</v>
       </c>
       <c r="F22" s="1">
-        <v>12514700</v>
+        <v>6767786.5</v>
       </c>
       <c r="G22" s="1">
-        <v>0.024190908297896385</v>
+        <v>0.14951774477958679</v>
       </c>
       <c r="H22" s="1"/>
       <c r="I22" t="s">
@@ -3824,22 +3824,22 @@
         <v>33679876</v>
       </c>
       <c r="B23" s="2">
-        <v>3868396111.2462006</v>
+        <v>527357973.86018229</v>
       </c>
       <c r="C23" s="2">
-        <v>7706861398654976</v>
+        <v>865487718187008</v>
       </c>
       <c r="D23" s="1">
         <v>0.99980467557907105</v>
       </c>
       <c r="E23" s="2">
-        <v>7706861941.9364643</v>
+        <v>865487734.30612576</v>
       </c>
       <c r="F23" s="1">
-        <v>12514700</v>
+        <v>6767786.5</v>
       </c>
       <c r="G23" s="1">
-        <v>0.018047519028186798</v>
+        <v>0.15034963190555573</v>
       </c>
       <c r="H23" s="1"/>
       <c r="I23" t="s">
@@ -3889,22 +3889,22 @@
         <v>34643400</v>
       </c>
       <c r="B2" s="2">
-        <v>11594973.7496546</v>
+        <v>10840086.272040302</v>
       </c>
       <c r="C2" s="2">
-        <v>133201599135744</v>
+        <v>72494224506880</v>
       </c>
       <c r="D2" s="1">
         <v>0.90007615089416504</v>
       </c>
       <c r="E2" s="2">
-        <v>21647279.352597456</v>
+        <v>19480637.022878569</v>
       </c>
       <c r="F2" s="1">
-        <v>13330037</v>
+        <v>7261452</v>
       </c>
       <c r="G2" s="1">
-        <v>0.00046175744500942528</v>
+        <v>0.00051221507601439953</v>
       </c>
       <c r="H2" s="1">
         <v>2019</v>
@@ -3918,22 +3918,22 @@
         <v>34643400</v>
       </c>
       <c r="B3" s="2">
-        <v>30657803.970223326</v>
+        <v>27561040.850124203</v>
       </c>
       <c r="C3" s="2">
-        <v>145509851332608</v>
+        <v>78343433093120</v>
       </c>
       <c r="D3" s="1">
         <v>0.91000562906265259</v>
       </c>
       <c r="E3" s="2">
-        <v>37781388.91068121</v>
+        <v>33639239.612957805</v>
       </c>
       <c r="F3" s="1">
-        <v>13330037</v>
+        <v>7261452</v>
       </c>
       <c r="G3" s="1">
-        <v>0.00059412239352241159</v>
+        <v>0.0006800949340686202</v>
       </c>
       <c r="H3" s="1"/>
       <c r="I3" t="s">
@@ -3945,22 +3945,22 @@
         <v>34643400</v>
       </c>
       <c r="B4" s="2">
-        <v>44314872.334533371</v>
+        <v>39180733.37013524</v>
       </c>
       <c r="C4" s="2">
-        <v>159028747436032</v>
+        <v>83971895459840</v>
       </c>
       <c r="D4" s="1">
-        <v>0.92003989219665527</v>
+        <v>0.92006927728652954</v>
       </c>
       <c r="E4" s="2">
-        <v>48994146.054838434</v>
+        <v>43209974.032943979</v>
       </c>
       <c r="F4" s="1">
-        <v>13330037</v>
+        <v>7261452</v>
       </c>
       <c r="G4" s="1">
-        <v>0.0012012382503598928</v>
+        <v>0.0015289017464965582</v>
       </c>
       <c r="H4" s="1"/>
       <c r="I4" t="s">
@@ -3972,22 +3972,22 @@
         <v>34643400</v>
       </c>
       <c r="B5" s="2">
-        <v>53028911.658820271</v>
+        <v>46831076.459303916</v>
       </c>
       <c r="C5" s="2">
-        <v>174817634418688</v>
+        <v>89803185979392</v>
       </c>
       <c r="D5" s="1">
-        <v>0.93007361888885498</v>
+        <v>0.9300728440284729</v>
       </c>
       <c r="E5" s="2">
-        <v>57141241.226837583</v>
+        <v>50167169.09935382</v>
       </c>
       <c r="F5" s="1">
-        <v>13330037</v>
+        <v>7261452</v>
       </c>
       <c r="G5" s="1">
-        <v>0.0020132798235863447</v>
+        <v>0.0022521698847413063</v>
       </c>
       <c r="H5" s="1"/>
       <c r="I5" t="s">
@@ -3999,22 +3999,22 @@
         <v>34643400</v>
       </c>
       <c r="B6" s="2">
-        <v>61479721.212121211</v>
+        <v>53240941.809156097</v>
       </c>
       <c r="C6" s="2">
-        <v>194293314617344</v>
+        <v>96370501353472</v>
       </c>
       <c r="D6" s="1">
-        <v>0.94000321626663208</v>
+        <v>0.94001227617263794</v>
       </c>
       <c r="E6" s="2">
-        <v>66119612.120374314</v>
+        <v>56427297.581669003</v>
       </c>
       <c r="F6" s="1">
-        <v>13330037</v>
+        <v>7261452</v>
       </c>
       <c r="G6" s="1">
-        <v>0.0046322885900735855</v>
+        <v>0.0054398500360548496</v>
       </c>
       <c r="H6" s="1"/>
       <c r="I6" t="s">
@@ -4026,22 +4026,22 @@
         <v>34643400</v>
       </c>
       <c r="B7" s="2">
-        <v>71380637.438152835</v>
+        <v>60037146.334716462</v>
       </c>
       <c r="C7" s="2">
-        <v>220035435986944</v>
+        <v>104384859996160</v>
       </c>
       <c r="D7" s="1">
-        <v>0.95003753900527954</v>
+        <v>0.95003706216812134</v>
       </c>
       <c r="E7" s="2">
-        <v>77814264.711198568</v>
+        <v>63794419.394545078</v>
       </c>
       <c r="F7" s="1">
-        <v>13330037</v>
+        <v>7261452</v>
       </c>
       <c r="G7" s="1">
-        <v>0.010105748660862446</v>
+        <v>0.01232418604195118</v>
       </c>
       <c r="H7" s="1"/>
       <c r="I7" t="s">
@@ -4053,22 +4053,22 @@
         <v>34643400</v>
       </c>
       <c r="B8" s="2">
-        <v>85187455.472842574</v>
+        <v>67631584.433443367</v>
       </c>
       <c r="C8" s="2">
-        <v>255776090226688</v>
+        <v>114587923906560</v>
       </c>
       <c r="D8" s="1">
-        <v>0.96007168292999268</v>
+        <v>0.96007323265075684</v>
       </c>
       <c r="E8" s="2">
-        <v>93987653.904089436</v>
+        <v>72533878.777510062</v>
       </c>
       <c r="F8" s="1">
-        <v>13330037</v>
+        <v>7261452</v>
       </c>
       <c r="G8" s="1">
-        <v>0.01516744215041399</v>
+        <v>0.020315643399953842</v>
       </c>
       <c r="H8" s="1"/>
       <c r="I8" t="s">
@@ -4080,22 +4080,22 @@
         <v>34643400</v>
       </c>
       <c r="B9" s="2">
-        <v>104044776.39922801</v>
+        <v>77239347.862068966</v>
       </c>
       <c r="C9" s="2">
-        <v>309330859524096</v>
+        <v>128693074657280</v>
       </c>
       <c r="D9" s="1">
-        <v>0.97000163793563843</v>
+        <v>0.97010141611099243</v>
       </c>
       <c r="E9" s="2">
-        <v>118428857.08018701</v>
+        <v>84478511.41685842</v>
       </c>
       <c r="F9" s="1">
-        <v>13330037</v>
+        <v>7261452</v>
       </c>
       <c r="G9" s="1">
-        <v>0.02141517773270607</v>
+        <v>0.029485287144780159</v>
       </c>
       <c r="H9" s="1"/>
       <c r="I9" t="s">
@@ -4107,22 +4107,22 @@
         <v>34643400</v>
       </c>
       <c r="B10" s="2">
-        <v>136853564.68965518</v>
+        <v>97450844.112769499</v>
       </c>
       <c r="C10" s="2">
-        <v>405282844835840</v>
+        <v>150696879980544</v>
       </c>
       <c r="D10" s="1">
-        <v>0.98003602027893067</v>
+        <v>0.98003643751144409</v>
       </c>
       <c r="E10" s="2">
-        <v>170601940.21926117</v>
+        <v>111387021.4817308</v>
       </c>
       <c r="F10" s="1">
-        <v>13330037</v>
+        <v>7261452</v>
       </c>
       <c r="G10" s="1">
-        <v>0.035045720636844635</v>
+        <v>0.053724590688943863</v>
       </c>
       <c r="H10" s="1"/>
       <c r="I10" t="s">
@@ -4134,22 +4134,22 @@
         <v>34643400</v>
       </c>
       <c r="B11" s="2">
-        <v>221380180.43658468</v>
+        <v>128957994.20049712</v>
       </c>
       <c r="C11" s="2">
-        <v>642436107862016</v>
+        <v>190419153453056</v>
       </c>
       <c r="D11" s="1">
         <v>0.99007034301757813</v>
       </c>
       <c r="E11" s="2">
-        <v>228311577.29965317</v>
+        <v>131043989.77199495</v>
       </c>
       <c r="F11" s="1">
-        <v>13330037</v>
+        <v>7261452</v>
       </c>
       <c r="G11" s="1">
-        <v>0.040303111076354981</v>
+        <v>0.070260792970657349</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" t="s">
@@ -4161,22 +4161,22 @@
         <v>34643400</v>
       </c>
       <c r="B12" s="2">
-        <v>237479977.40424359</v>
+        <v>133372696.08059616</v>
       </c>
       <c r="C12" s="2">
-        <v>685762462875648</v>
+        <v>196632343740416</v>
       </c>
       <c r="D12" s="1">
-        <v>0.99101078510284424</v>
+        <v>0.99101096391677857</v>
       </c>
       <c r="E12" s="2">
-        <v>246720303.73560837</v>
+        <v>135745461.60218707</v>
       </c>
       <c r="F12" s="1">
-        <v>13330037</v>
+        <v>7261452</v>
       </c>
       <c r="G12" s="1">
-        <v>0.040612787008285523</v>
+        <v>0.073555760085582733</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" t="s">
@@ -4188,22 +4188,22 @@
         <v>34643400</v>
       </c>
       <c r="B13" s="2">
-        <v>258767053.85252693</v>
+        <v>140552096.9345485</v>
       </c>
       <c r="C13" s="2">
-        <v>743545140936704</v>
+        <v>204644387127296</v>
       </c>
       <c r="D13" s="1">
         <v>0.99205625057220459</v>
       </c>
       <c r="E13" s="2">
-        <v>270348854.04181278</v>
+        <v>141913289.28837711</v>
       </c>
       <c r="F13" s="1">
-        <v>13330037</v>
+        <v>7261452</v>
       </c>
       <c r="G13" s="1">
-        <v>0.041340947151184082</v>
+        <v>0.078930877149105072</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" t="s">
@@ -4215,22 +4215,22 @@
         <v>34643400</v>
       </c>
       <c r="B14" s="2">
-        <v>285489657.30461198</v>
+        <v>146196830.15741515</v>
       </c>
       <c r="C14" s="2">
-        <v>815238748307456</v>
+        <v>214149938282496</v>
       </c>
       <c r="D14" s="1">
-        <v>0.99310147762298584</v>
+        <v>0.99310159683227539</v>
       </c>
       <c r="E14" s="2">
-        <v>298009095.64296889</v>
+        <v>148864993.58946818</v>
       </c>
       <c r="F14" s="1">
-        <v>13330037</v>
+        <v>7261452</v>
       </c>
       <c r="G14" s="1">
-        <v>0.042402900755405426</v>
+        <v>0.084540136158466339</v>
       </c>
       <c r="H14" s="1"/>
       <c r="I14" t="s">
@@ -4242,22 +4242,22 @@
         <v>34643400</v>
       </c>
       <c r="B15" s="2">
-        <v>315105727.00911349</v>
+        <v>154502663.81215474</v>
       </c>
       <c r="C15" s="2">
-        <v>896911175319552</v>
+        <v>224457390030848</v>
       </c>
       <c r="D15" s="1">
         <v>0.99404221773147583</v>
       </c>
       <c r="E15" s="2">
-        <v>333780602.22314274</v>
+        <v>157279807.92598727</v>
       </c>
       <c r="F15" s="1">
-        <v>13330037</v>
+        <v>7261452</v>
       </c>
       <c r="G15" s="1">
-        <v>0.043095212429761887</v>
+        <v>0.092955909669399261</v>
       </c>
       <c r="H15" s="1"/>
       <c r="I15" t="s">
@@ -4269,22 +4269,22 @@
         <v>34643400</v>
       </c>
       <c r="B16" s="2">
-        <v>359252194.19889504</v>
+        <v>161143196.63076502</v>
       </c>
       <c r="C16" s="2">
-        <v>1016725462056960</v>
+        <v>238750420434944</v>
       </c>
       <c r="D16" s="1">
         <v>0.99508744478225708</v>
       </c>
       <c r="E16" s="2">
-        <v>381316343.02985668</v>
+        <v>169176636.96339256</v>
       </c>
       <c r="F16" s="1">
-        <v>13330037</v>
+        <v>7261452</v>
       </c>
       <c r="G16" s="1">
-        <v>0.045939598232507706</v>
+        <v>0.1012209951877594</v>
       </c>
       <c r="H16" s="1"/>
       <c r="I16" t="s">
@@ -4296,22 +4296,22 @@
         <v>34643400</v>
       </c>
       <c r="B17" s="2">
-        <v>412167688.29376036</v>
+        <v>174207513.80452794</v>
       </c>
       <c r="C17" s="2">
-        <v>1167216015835136</v>
+        <v>255228280569856</v>
       </c>
       <c r="D17" s="1">
         <v>0.99602812528610229</v>
       </c>
       <c r="E17" s="2">
-        <v>448748645.05260837</v>
+        <v>178713966.39142802</v>
       </c>
       <c r="F17" s="1">
-        <v>13330037</v>
+        <v>7261452</v>
       </c>
       <c r="G17" s="1">
-        <v>0.04303356260061264</v>
+        <v>0.10724449902772903</v>
       </c>
       <c r="H17" s="1"/>
       <c r="I17" t="s">
@@ -4323,22 +4323,22 @@
         <v>34643400</v>
       </c>
       <c r="B18" s="2">
-        <v>497738088.92571116</v>
+        <v>185442980.11599007</v>
       </c>
       <c r="C18" s="2">
-        <v>1423818434281472</v>
+        <v>282555597193216</v>
       </c>
       <c r="D18" s="1">
         <v>0.99707335233688355</v>
       </c>
       <c r="E18" s="2">
-        <v>555166538.15704679</v>
+        <v>201231241.64595416</v>
       </c>
       <c r="F18" s="1">
-        <v>13330037</v>
+        <v>7261452</v>
       </c>
       <c r="G18" s="1">
-        <v>0.0425751693546772</v>
+        <v>0.11882581561803818</v>
       </c>
       <c r="H18" s="1"/>
       <c r="I18" t="s">
@@ -4350,22 +4350,22 @@
         <v>34643400</v>
       </c>
       <c r="B19" s="2">
-        <v>647181541.56310415</v>
+        <v>214781254.07346028</v>
       </c>
       <c r="C19" s="2">
-        <v>1835285293826048</v>
+        <v>321077662187520</v>
       </c>
       <c r="D19" s="1">
         <v>0.99801409244537354</v>
       </c>
       <c r="E19" s="2">
-        <v>830300168.58728135</v>
+        <v>230954776.4806307</v>
       </c>
       <c r="F19" s="1">
-        <v>13330037</v>
+        <v>7261452</v>
       </c>
       <c r="G19" s="1">
-        <v>0.039665382355451584</v>
+        <v>0.14093506336212158</v>
       </c>
       <c r="H19" s="1"/>
       <c r="I19" t="s">
@@ -4377,22 +4377,22 @@
         <v>34643400</v>
       </c>
       <c r="B20" s="2">
-        <v>1203743483.8442421</v>
+        <v>269722231.42778248</v>
       </c>
       <c r="C20" s="2">
-        <v>3217139884359680</v>
+        <v>444996595482624</v>
       </c>
       <c r="D20" s="1">
         <v>0.99916380643844605</v>
       </c>
       <c r="E20" s="2">
-        <v>1267855164.8853908</v>
+        <v>278218451.8599835</v>
       </c>
       <c r="F20" s="1">
-        <v>13330037</v>
+        <v>7261452</v>
       </c>
       <c r="G20" s="1">
-        <v>0.035440489649772644</v>
+        <v>0.16692966222763062</v>
       </c>
       <c r="H20" s="1"/>
       <c r="I20" t="s">
@@ -4404,22 +4404,22 @@
         <v>34643400</v>
       </c>
       <c r="B21" s="2">
-        <v>1498320625.5788457</v>
+        <v>291887626.37393004</v>
       </c>
       <c r="C21" s="2">
-        <v>3866901595815936</v>
+        <v>500589309984768</v>
       </c>
       <c r="D21" s="1">
         <v>0.99937283992767334</v>
       </c>
       <c r="E21" s="2">
-        <v>1612641195.0042808</v>
+        <v>306546948.92294943</v>
       </c>
       <c r="F21" s="1">
-        <v>13330037</v>
+        <v>7261452</v>
       </c>
       <c r="G21" s="1">
-        <v>0.03249678760766983</v>
+        <v>0.16521260142326355</v>
       </c>
       <c r="H21" s="1"/>
       <c r="I21" t="s">
@@ -4431,22 +4431,22 @@
         <v>34643400</v>
       </c>
       <c r="B22" s="2">
-        <v>2064428890.3617785</v>
+        <v>340582888.15244412</v>
       </c>
       <c r="C22" s="2">
-        <v>4994031742353408</v>
+        <v>597610473717760</v>
       </c>
       <c r="D22" s="1">
         <v>0.99958193302154541</v>
       </c>
       <c r="E22" s="2">
-        <v>2337191024.9930959</v>
+        <v>357608056.33802831</v>
       </c>
       <c r="F22" s="1">
-        <v>13330037</v>
+        <v>7261452</v>
       </c>
       <c r="G22" s="1">
-        <v>0.027836818248033524</v>
+        <v>0.18049910664558411</v>
       </c>
       <c r="H22" s="1"/>
       <c r="I22" t="s">
@@ -4458,22 +4458,22 @@
         <v>34643400</v>
       </c>
       <c r="B23" s="2">
-        <v>3729339323.7503452</v>
+        <v>482351231.12399894</v>
       </c>
       <c r="C23" s="2">
-        <v>7650871668113408</v>
+        <v>837612910673920</v>
       </c>
       <c r="D23" s="1">
         <v>0.99979096651077271</v>
       </c>
       <c r="E23" s="2">
-        <v>7650871693.040596</v>
+        <v>837612941.10742974</v>
       </c>
       <c r="F23" s="1">
-        <v>13330037</v>
+        <v>7261452</v>
       </c>
       <c r="G23" s="1">
-        <v>0.020835340023040771</v>
+        <v>0.17796653509140015</v>
       </c>
       <c r="H23" s="1"/>
       <c r="I23" t="s">
@@ -4486,7 +4486,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4523,22 +4523,22 @@
         <v>35465232</v>
       </c>
       <c r="B2" s="2">
-        <v>1235685.8864892013</v>
+        <v>21312112.449799191</v>
       </c>
       <c r="C2" s="2">
-        <v>121358293925888</v>
+        <v>75420556853248</v>
       </c>
       <c r="D2" s="1">
-        <v>0.89003574848175049</v>
+        <v>0.90001267194747925</v>
       </c>
       <c r="E2" s="2">
-        <v>13842837.980131991</v>
+        <v>27476471.717126079</v>
       </c>
       <c r="F2" s="1">
-        <v>13345300</v>
+        <v>7666648</v>
       </c>
       <c r="G2" s="1">
-        <v>0.00037170693394728005</v>
+        <v>0.00010064633534057066</v>
       </c>
       <c r="H2" s="1">
         <v>2020</v>
@@ -4552,22 +4552,22 @@
         <v>35465232</v>
       </c>
       <c r="B3" s="2">
-        <v>23235456.268958543</v>
+        <v>33409617.436404049</v>
       </c>
       <c r="C3" s="2">
-        <v>132086425976832</v>
+        <v>80799349080064</v>
       </c>
       <c r="D3" s="1">
-        <v>0.90001267194747925</v>
+        <v>0.9100986123085022</v>
       </c>
       <c r="E3" s="2">
-        <v>30221914.935351063</v>
+        <v>37935193.432252854</v>
       </c>
       <c r="F3" s="1">
-        <v>13345300</v>
+        <v>7666648</v>
       </c>
       <c r="G3" s="1">
-        <v>9.1200919996481389e-05</v>
+        <v>0.00078340602340176702</v>
       </c>
       <c r="H3" s="1"/>
       <c r="I3" t="s">
@@ -4579,22 +4579,22 @@
         <v>35465232</v>
       </c>
       <c r="B4" s="2">
-        <v>36807173.858504765</v>
+        <v>42427452.232476927</v>
       </c>
       <c r="C4" s="2">
-        <v>143516734849024</v>
+        <v>86149880086528</v>
       </c>
       <c r="D4" s="1">
-        <v>0.91010040044784546</v>
+        <v>0.92007523775100708</v>
       </c>
       <c r="E4" s="2">
-        <v>41933553.036528327</v>
+        <v>45459518.870648727</v>
       </c>
       <c r="F4" s="1">
-        <v>13345300</v>
+        <v>7666648</v>
       </c>
       <c r="G4" s="1">
-        <v>0.00070044706808403134</v>
+        <v>0.0013312867376953363</v>
       </c>
       <c r="H4" s="1"/>
       <c r="I4" t="s">
@@ -4606,22 +4606,22 @@
         <v>35465232</v>
       </c>
       <c r="B5" s="2">
-        <v>47101244.820616476</v>
+        <v>49047968.639352553</v>
       </c>
       <c r="C5" s="2">
-        <v>156197625790464</v>
+        <v>91955308527616</v>
       </c>
       <c r="D5" s="1">
-        <v>0.920077383518219</v>
+        <v>0.93005460500717163</v>
       </c>
       <c r="E5" s="2">
-        <v>51133847.296953537</v>
+        <v>51775726.1599316</v>
       </c>
       <c r="F5" s="1">
-        <v>13345300</v>
+        <v>7666648</v>
       </c>
       <c r="G5" s="1">
-        <v>0.0011573371011763811</v>
+        <v>0.0021996593568474054</v>
       </c>
       <c r="H5" s="1"/>
       <c r="I5" t="s">
@@ -4633,22 +4633,22 @@
         <v>35465232</v>
       </c>
       <c r="B6" s="2">
-        <v>54917567.283641823</v>
+        <v>54795113.40206185</v>
       </c>
       <c r="C6" s="2">
-        <v>171181407731712</v>
+        <v>98638009204736</v>
       </c>
       <c r="D6" s="1">
-        <v>0.93005293607711792</v>
+        <v>0.94002902507781982</v>
       </c>
       <c r="E6" s="2">
-        <v>58928098.083012573</v>
+        <v>58038846.230748817</v>
       </c>
       <c r="F6" s="1">
-        <v>13345300</v>
+        <v>7666648</v>
       </c>
       <c r="G6" s="1">
-        <v>0.0019341743318364024</v>
+        <v>0.0047328798100352287</v>
       </c>
       <c r="H6" s="1"/>
       <c r="I6" t="s">
@@ -4660,22 +4660,22 @@
         <v>35465232</v>
       </c>
       <c r="B7" s="2">
-        <v>63204799.849132516</v>
+        <v>61652844.522968203</v>
       </c>
       <c r="C7" s="2">
-        <v>189856663732224</v>
+        <v>106750447452160</v>
       </c>
       <c r="D7" s="1">
-        <v>0.94002997875213623</v>
+        <v>0.95001661777496338</v>
       </c>
       <c r="E7" s="2">
-        <v>67821411.75952901</v>
+        <v>65316914.77703552</v>
       </c>
       <c r="F7" s="1">
-        <v>13345300</v>
+        <v>7666648</v>
       </c>
       <c r="G7" s="1">
-        <v>0.0039875688962638378</v>
+        <v>0.011275664903223515</v>
       </c>
       <c r="H7" s="1"/>
       <c r="I7" t="s">
@@ -4687,22 +4687,22 @@
         <v>35465232</v>
       </c>
       <c r="B8" s="2">
-        <v>72846796.803652972</v>
+        <v>69122733.686067015</v>
       </c>
       <c r="C8" s="2">
-        <v>214209111523328</v>
+        <v>117233028169728</v>
       </c>
       <c r="D8" s="1">
-        <v>0.95000630617141724</v>
+        <v>0.96010893583297729</v>
       </c>
       <c r="E8" s="2">
-        <v>79083304.364560261</v>
+        <v>74140658.391932488</v>
       </c>
       <c r="F8" s="1">
-        <v>13345300</v>
+        <v>7666648</v>
       </c>
       <c r="G8" s="1">
-        <v>0.0092853009700775146</v>
+        <v>0.019278550520539284</v>
       </c>
       <c r="H8" s="1"/>
       <c r="I8" t="s">
@@ -4714,22 +4714,22 @@
         <v>35465232</v>
       </c>
       <c r="B9" s="2">
-        <v>86185291.437155738</v>
+        <v>80923762.264150947</v>
       </c>
       <c r="C9" s="2">
-        <v>248367758180352</v>
+        <v>131582606180352</v>
       </c>
       <c r="D9" s="1">
-        <v>0.96009421348571777</v>
+        <v>0.9700741171836853</v>
       </c>
       <c r="E9" s="2">
-        <v>94955252.960913435</v>
+        <v>85880039.42167592</v>
       </c>
       <c r="F9" s="1">
-        <v>13345300</v>
+        <v>7666648</v>
       </c>
       <c r="G9" s="1">
-        <v>0.014628463424742222</v>
+        <v>0.026947168633341789</v>
       </c>
       <c r="H9" s="1"/>
       <c r="I9" t="s">
@@ -4741,22 +4741,22 @@
         <v>35465232</v>
       </c>
       <c r="B10" s="2">
-        <v>104854033.27451475</v>
+        <v>97883164.531524733</v>
       </c>
       <c r="C10" s="2">
-        <v>299507698892800</v>
+        <v>154429340778496</v>
       </c>
       <c r="D10" s="1">
-        <v>0.97007101774215698</v>
+        <v>0.98004812002182007</v>
       </c>
       <c r="E10" s="2">
-        <v>118239273.60840569</v>
+        <v>113266809.0042343</v>
       </c>
       <c r="F10" s="1">
-        <v>13345300</v>
+        <v>7666648</v>
       </c>
       <c r="G10" s="1">
-        <v>0.019930940121412277</v>
+        <v>0.050156492739915848</v>
       </c>
       <c r="H10" s="1"/>
       <c r="I10" t="s">
@@ -4768,22 +4768,22 @@
         <v>35465232</v>
       </c>
       <c r="B11" s="2">
-        <v>135705921.54890621</v>
+        <v>131970473.98843929</v>
       </c>
       <c r="C11" s="2">
-        <v>390140769861632</v>
+        <v>195586871525376</v>
       </c>
       <c r="D11" s="1">
-        <v>0.98004722595214844</v>
+        <v>0.99002343416213989</v>
       </c>
       <c r="E11" s="2">
-        <v>167079938.09826627</v>
+        <v>132677694.98155807</v>
       </c>
       <c r="F11" s="1">
-        <v>13345300</v>
+        <v>7666648</v>
       </c>
       <c r="G11" s="1">
-        <v>0.033949006348848343</v>
+        <v>0.067371979355812073</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" t="s">
@@ -4795,22 +4795,22 @@
         <v>35465232</v>
       </c>
       <c r="B12" s="2">
-        <v>214217687.97181681</v>
+        <v>135240592.65778223</v>
       </c>
       <c r="C12" s="2">
-        <v>613201003675648</v>
+        <v>202665984262144</v>
       </c>
       <c r="D12" s="1">
-        <v>0.99002361297607422</v>
+        <v>0.99103254079818726</v>
       </c>
       <c r="E12" s="2">
-        <v>220947174.7016573</v>
+        <v>136886485.11613608</v>
       </c>
       <c r="F12" s="1">
-        <v>13345300</v>
+        <v>7666648</v>
       </c>
       <c r="G12" s="1">
-        <v>0.040319833904504776</v>
+        <v>0.06991143524646759</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" t="s">
@@ -4822,22 +4822,22 @@
         <v>35465232</v>
       </c>
       <c r="B13" s="2">
-        <v>230115107.19677907</v>
+        <v>141307732.64587525</v>
       </c>
       <c r="C13" s="2">
-        <v>657332195295232</v>
+        <v>211003790852096</v>
       </c>
       <c r="D13" s="1">
-        <v>0.99103254079818726</v>
+        <v>0.99204134941101074</v>
       </c>
       <c r="E13" s="2">
-        <v>238387571.3247624</v>
+        <v>143975064.27420351</v>
       </c>
       <c r="F13" s="1">
-        <v>13345300</v>
+        <v>7666648</v>
       </c>
       <c r="G13" s="1">
-        <v>0.040482118725776672</v>
+        <v>0.074990123510360718</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" t="s">
@@ -4849,22 +4849,22 @@
         <v>35465232</v>
       </c>
       <c r="B14" s="2">
-        <v>249415860.09058884</v>
+        <v>147660567.79874215</v>
       </c>
       <c r="C14" s="2">
-        <v>710439868563456</v>
+        <v>220734089592832</v>
       </c>
       <c r="D14" s="1">
-        <v>0.99204140901565552</v>
+        <v>0.993050217628479</v>
       </c>
       <c r="E14" s="2">
-        <v>259519672.02557439</v>
+        <v>149756181.60093907</v>
       </c>
       <c r="F14" s="1">
-        <v>13345300</v>
+        <v>7666648</v>
       </c>
       <c r="G14" s="1">
-        <v>0.04131559282541275</v>
+        <v>0.07994687557220459</v>
       </c>
       <c r="H14" s="1"/>
       <c r="I14" t="s">
@@ -4876,22 +4876,22 @@
         <v>35465232</v>
       </c>
       <c r="B15" s="2">
-        <v>273377526.40845066</v>
+        <v>153897646.37826961</v>
       </c>
       <c r="C15" s="2">
-        <v>775894566174720</v>
+        <v>232787042893824</v>
       </c>
       <c r="D15" s="1">
-        <v>0.993050217628479</v>
+        <v>0.99405902624130249</v>
       </c>
       <c r="E15" s="2">
-        <v>286155277.59300148</v>
+        <v>158778695.81865949</v>
       </c>
       <c r="F15" s="1">
-        <v>13345300</v>
+        <v>7666648</v>
       </c>
       <c r="G15" s="1">
-        <v>0.041925471276044846</v>
+        <v>0.086942575871944427</v>
       </c>
       <c r="H15" s="1"/>
       <c r="I15" t="s">
@@ -4903,22 +4903,22 @@
         <v>35465232</v>
       </c>
       <c r="B16" s="2">
-        <v>303426917.25352115</v>
+        <v>165458873.7424548</v>
       </c>
       <c r="C16" s="2">
-        <v>859058487689216</v>
+        <v>247924739014656</v>
       </c>
       <c r="D16" s="1">
-        <v>0.99405902624130249</v>
+        <v>0.99506789445877075</v>
       </c>
       <c r="E16" s="2">
-        <v>320045373.46973008</v>
+        <v>169412271.41619384</v>
       </c>
       <c r="F16" s="1">
-        <v>13345300</v>
+        <v>7666648</v>
       </c>
       <c r="G16" s="1">
-        <v>0.043011736124753952</v>
+        <v>0.094932578504085541</v>
       </c>
       <c r="H16" s="1"/>
       <c r="I16" t="s">
@@ -4930,22 +4930,22 @@
         <v>35465232</v>
       </c>
       <c r="B17" s="2">
-        <v>343445075.43374401</v>
+        <v>178389287.22334006</v>
       </c>
       <c r="C17" s="2">
-        <v>969308419129344</v>
+        <v>268113736105984</v>
       </c>
       <c r="D17" s="1">
-        <v>0.99506789445877075</v>
+        <v>0.99607670307159424</v>
       </c>
       <c r="E17" s="2">
-        <v>366613975.57294577</v>
+        <v>182880705.63359419</v>
       </c>
       <c r="F17" s="1">
-        <v>13345300</v>
+        <v>7666648</v>
       </c>
       <c r="G17" s="1">
-        <v>0.043940853327512741</v>
+        <v>0.10213737934827805</v>
       </c>
       <c r="H17" s="1"/>
       <c r="I17" t="s">
@@ -4957,22 +4957,22 @@
         <v>35465232</v>
       </c>
       <c r="B18" s="2">
-        <v>398764448.3018868</v>
+        <v>188534480.50314462</v>
       </c>
       <c r="C18" s="2">
-        <v>1124293119311872</v>
+        <v>297618752143360</v>
       </c>
       <c r="D18" s="1">
-        <v>0.99607676267623901</v>
+        <v>0.9970855712890625</v>
       </c>
       <c r="E18" s="2">
-        <v>431834393.01182258</v>
+        <v>207517734.16624743</v>
       </c>
       <c r="F18" s="1">
-        <v>13345300</v>
+        <v>7666648</v>
       </c>
       <c r="G18" s="1">
-        <v>0.043348178267478943</v>
+        <v>0.11156893521547318</v>
       </c>
       <c r="H18" s="1"/>
       <c r="I18" t="s">
@@ -4984,22 +4984,22 @@
         <v>35465232</v>
       </c>
       <c r="B19" s="2">
-        <v>480210993.71069181</v>
+        <v>223005288.98390353</v>
       </c>
       <c r="C19" s="2">
-        <v>1363993969033216</v>
+        <v>345318323388416</v>
       </c>
       <c r="D19" s="1">
-        <v>0.9970855712890625</v>
+        <v>0.99809443950653076</v>
       </c>
       <c r="E19" s="2">
-        <v>536201609.62043715</v>
+        <v>241095941.66969451</v>
       </c>
       <c r="F19" s="1">
-        <v>13345300</v>
+        <v>7666648</v>
       </c>
       <c r="G19" s="1">
-        <v>0.043111559003591538</v>
+        <v>0.13169223070144653</v>
       </c>
       <c r="H19" s="1"/>
       <c r="I19" t="s">
@@ -5011,22 +5011,22 @@
         <v>35465232</v>
       </c>
       <c r="B20" s="2">
-        <v>634900341.04627764</v>
+        <v>279499444.66800803</v>
       </c>
       <c r="C20" s="2">
-        <v>1802228272726016</v>
+        <v>462570561470464</v>
       </c>
       <c r="D20" s="1">
-        <v>0.99809443950653076</v>
+        <v>0.99910324811935425</v>
       </c>
       <c r="E20" s="2">
-        <v>788741096.59297359</v>
+        <v>284056269.65161622</v>
       </c>
       <c r="F20" s="1">
-        <v>13345300</v>
+        <v>7666648</v>
       </c>
       <c r="G20" s="1">
-        <v>0.040660012513399124</v>
+        <v>0.14814381301403046</v>
       </c>
       <c r="H20" s="1"/>
       <c r="I20" t="s">
@@ -5038,22 +5038,22 @@
         <v>35465232</v>
       </c>
       <c r="B21" s="2">
-        <v>1089642781.1871228</v>
+        <v>309227215.84905654</v>
       </c>
       <c r="C21" s="2">
-        <v>2942421159641088</v>
+        <v>522077836673024</v>
       </c>
       <c r="D21" s="1">
-        <v>0.99910324811935425</v>
+        <v>0.99932748079299927</v>
       </c>
       <c r="E21" s="2">
-        <v>1148527452.8990064</v>
+        <v>318292896.36523718</v>
       </c>
       <c r="F21" s="1">
-        <v>13345300</v>
+        <v>7666648</v>
       </c>
       <c r="G21" s="1">
-        <v>0.036707356572151184</v>
+        <v>0.15544717013835907</v>
       </c>
       <c r="H21" s="1"/>
       <c r="I21" t="s">
@@ -5065,22 +5065,22 @@
         <v>35465232</v>
       </c>
       <c r="B22" s="2">
-        <v>1357788757.2327044</v>
+        <v>367356349.18239009</v>
       </c>
       <c r="C22" s="2">
-        <v>3540410798440448</v>
+        <v>623976673968128</v>
       </c>
       <c r="D22" s="1">
-        <v>0.99932748079299927</v>
+        <v>0.99955165386199951</v>
       </c>
       <c r="E22" s="2">
-        <v>1461935758.5209408</v>
+        <v>391162171.32197207</v>
       </c>
       <c r="F22" s="1">
-        <v>13345300</v>
+        <v>7666648</v>
       </c>
       <c r="G22" s="1">
-        <v>0.033884212374687195</v>
+        <v>0.1610887199640274</v>
       </c>
       <c r="H22" s="1"/>
       <c r="I22" t="s">
@@ -5092,52 +5092,25 @@
         <v>35465232</v>
       </c>
       <c r="B23" s="2">
-        <v>1871512726.5408804</v>
+        <v>506648716.22641516</v>
       </c>
       <c r="C23" s="2">
-        <v>4579713964048384</v>
+        <v>856820541292544</v>
       </c>
       <c r="D23" s="1">
-        <v>0.99955165386199951</v>
+        <v>0.99977582693099976</v>
       </c>
       <c r="E23" s="2">
-        <v>2120783790.6151426</v>
+        <v>856820529.81132162</v>
       </c>
       <c r="F23" s="1">
-        <v>13345300</v>
+        <v>7666648</v>
       </c>
       <c r="G23" s="1">
-        <v>0.029867907986044884</v>
+        <v>0.17485350370407104</v>
       </c>
       <c r="H23" s="1"/>
       <c r="I23" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1">
-        <v>35465232</v>
-      </c>
-      <c r="B24" s="2">
-        <v>3379430312.2012577</v>
-      </c>
-      <c r="C24" s="2">
-        <v>7038953718808576</v>
-      </c>
-      <c r="D24" s="1">
-        <v>0.99977582693099976</v>
-      </c>
-      <c r="E24" s="2">
-        <v>7038953437.35849</v>
-      </c>
-      <c r="F24" s="1">
-        <v>13345300</v>
-      </c>
-      <c r="G24" s="1">
-        <v>0.023092702031135559</v>
-      </c>
-      <c r="H24" s="1"/>
-      <c r="I24" t="s">
         <v>10</v>
       </c>
     </row>
@@ -5184,22 +5157,22 @@
         <v>36138868</v>
       </c>
       <c r="B2" s="2">
-        <v>4937079.3972109761</v>
+        <v>4352948.4930274412</v>
       </c>
       <c r="C2" s="2">
-        <v>133868510248960</v>
+        <v>73581471989760</v>
       </c>
       <c r="D2" s="1">
         <v>0.88004446029663086</v>
       </c>
       <c r="E2" s="2">
-        <v>16242931.172368979</v>
+        <v>14957628.134745097</v>
       </c>
       <c r="F2" s="1">
-        <v>16060846</v>
+        <v>8828315</v>
       </c>
       <c r="G2" s="1">
-        <v>0.00013586577551905066</v>
+        <v>0.00014747306704521179</v>
       </c>
       <c r="H2" s="1">
         <v>2021</v>
@@ -5213,22 +5186,22 @@
         <v>36138868</v>
       </c>
       <c r="B3" s="2">
-        <v>25186818.141097423</v>
+        <v>23047694.512877937</v>
       </c>
       <c r="C3" s="2">
-        <v>144525028753408</v>
+        <v>78892601704448</v>
       </c>
       <c r="D3" s="1">
         <v>0.89000928401947021</v>
       </c>
       <c r="E3" s="2">
-        <v>31994406.925064888</v>
+        <v>29380753.632648587</v>
       </c>
       <c r="F3" s="1">
-        <v>16060846</v>
+        <v>8828315</v>
       </c>
       <c r="G3" s="1">
-        <v>7.6025404268875718e-05</v>
+        <v>8.2311184087302536e-05</v>
       </c>
       <c r="H3" s="1"/>
       <c r="I3" t="s">
@@ -5240,22 +5213,22 @@
         <v>36138868</v>
       </c>
       <c r="B4" s="2">
-        <v>38264292.08791209</v>
+        <v>35084754.203362696</v>
       </c>
       <c r="C4" s="2">
-        <v>155885854785536</v>
+        <v>83892841218048</v>
       </c>
       <c r="D4" s="1">
-        <v>0.90009540319442749</v>
+        <v>0.90009844303131104</v>
       </c>
       <c r="E4" s="2">
-        <v>42950857.811879724</v>
+        <v>39111984.841586255</v>
       </c>
       <c r="F4" s="1">
-        <v>16060846</v>
+        <v>8828315</v>
       </c>
       <c r="G4" s="1">
-        <v>0.00068043777719140053</v>
+        <v>0.00077051552943885326</v>
       </c>
       <c r="H4" s="1"/>
       <c r="I4" t="s">
@@ -5267,22 +5240,22 @@
         <v>36138868</v>
       </c>
       <c r="B5" s="2">
-        <v>47917852.781546809</v>
+        <v>43062727.211796239</v>
       </c>
       <c r="C5" s="2">
-        <v>168402647777280</v>
+        <v>88855675928576</v>
       </c>
       <c r="D5" s="1">
-        <v>0.91006326675415039</v>
+        <v>0.9100654125213623</v>
       </c>
       <c r="E5" s="2">
-        <v>51883671.14276588</v>
+        <v>46049067.442594104</v>
       </c>
       <c r="F5" s="1">
-        <v>16060846</v>
+        <v>8828315</v>
       </c>
       <c r="G5" s="1">
-        <v>0.0012063274625688791</v>
+        <v>0.0013798681320622563</v>
       </c>
       <c r="H5" s="1"/>
       <c r="I5" t="s">
@@ -5294,22 +5267,22 @@
         <v>36138868</v>
       </c>
       <c r="B6" s="2">
-        <v>55618742.760942765</v>
+        <v>49213257.239057243</v>
       </c>
       <c r="C6" s="2">
-        <v>182922204151808</v>
+        <v>94210636120064</v>
       </c>
       <c r="D6" s="1">
-        <v>0.92002856731414795</v>
+        <v>0.92006498575210571</v>
       </c>
       <c r="E6" s="2">
-        <v>59512895.340226538</v>
+        <v>51964660.650060311</v>
       </c>
       <c r="F6" s="1">
-        <v>16060846</v>
+        <v>8828315</v>
       </c>
       <c r="G6" s="1">
-        <v>0.0018889468628913164</v>
+        <v>0.0021992253605276346</v>
       </c>
       <c r="H6" s="1"/>
       <c r="I6" t="s">
@@ -5321,22 +5294,22 @@
         <v>36138868</v>
       </c>
       <c r="B7" s="2">
-        <v>63668408.305274971</v>
+        <v>54728734.569296867</v>
       </c>
       <c r="C7" s="2">
-        <v>200739221667840</v>
+        <v>100220713041920</v>
       </c>
       <c r="D7" s="1">
-        <v>0.93011772632598877</v>
+        <v>0.93002057075500488</v>
       </c>
       <c r="E7" s="2">
-        <v>68027959.639125019</v>
+        <v>57542489.652118653</v>
       </c>
       <c r="F7" s="1">
-        <v>16060846</v>
+        <v>8828315</v>
       </c>
       <c r="G7" s="1">
-        <v>0.0035551323089748621</v>
+        <v>0.0043450105004012585</v>
       </c>
       <c r="H7" s="1"/>
       <c r="I7" t="s">
@@ -5348,22 +5321,22 @@
         <v>36138868</v>
       </c>
       <c r="B8" s="2">
-        <v>72556109.071504802</v>
+        <v>61082687.064117</v>
       </c>
       <c r="C8" s="2">
-        <v>222794986029056</v>
+        <v>107387067301888</v>
       </c>
       <c r="D8" s="1">
-        <v>0.94007664918899536</v>
+        <v>0.94008177518844605</v>
       </c>
       <c r="E8" s="2">
-        <v>77982818.39169766</v>
+        <v>63836362.135200128</v>
       </c>
       <c r="F8" s="1">
-        <v>16060846</v>
+        <v>8828315</v>
       </c>
       <c r="G8" s="1">
-        <v>0.0076103862375020981</v>
+        <v>0.0092050898820161819</v>
       </c>
       <c r="H8" s="1"/>
       <c r="I8" t="s">
@@ -5375,22 +5348,22 @@
         <v>36138868</v>
       </c>
       <c r="B9" s="2">
-        <v>84008877.922661871</v>
+        <v>67186153.294486806</v>
       </c>
       <c r="C9" s="2">
-        <v>251704746442752</v>
+        <v>116078957035520</v>
       </c>
       <c r="D9" s="1">
-        <v>0.95004868507385254</v>
+        <v>0.9500507116317749</v>
       </c>
       <c r="E9" s="2">
-        <v>91202606.682234257</v>
+        <v>70474434.278718978</v>
       </c>
       <c r="F9" s="1">
-        <v>16060846</v>
+        <v>8828315</v>
       </c>
       <c r="G9" s="1">
-        <v>0.012396081350743771</v>
+        <v>0.016154799610376358</v>
       </c>
       <c r="H9" s="1"/>
       <c r="I9" t="s">
@@ -5402,22 +5375,22 @@
         <v>36138868</v>
       </c>
       <c r="B10" s="2">
-        <v>99315157.210136801</v>
+        <v>74699602.70574972</v>
       </c>
       <c r="C10" s="2">
-        <v>291707065204736</v>
+        <v>127449262194688</v>
       </c>
       <c r="D10" s="1">
-        <v>0.96001440286636353</v>
+        <v>0.96001893281936646</v>
       </c>
       <c r="E10" s="2">
-        <v>109392638.51267959</v>
+        <v>79745851.168444172</v>
       </c>
       <c r="F10" s="1">
-        <v>16060846</v>
+        <v>8828315</v>
       </c>
       <c r="G10" s="1">
-        <v>0.016371915116906166</v>
+        <v>0.0230299923568964</v>
       </c>
       <c r="H10" s="1"/>
       <c r="I10" t="s">
@@ -5429,22 +5402,22 @@
         <v>36138868</v>
       </c>
       <c r="B11" s="2">
-        <v>121053491.89554256</v>
+        <v>83236383.164983168</v>
       </c>
       <c r="C11" s="2">
-        <v>353230793998336</v>
+        <v>143541229584384</v>
       </c>
       <c r="D11" s="1">
-        <v>0.97010332345962524</v>
+        <v>0.970103919506073</v>
       </c>
       <c r="E11" s="2">
-        <v>137038344.71948803</v>
+        <v>93858576.529790908</v>
       </c>
       <c r="F11" s="1">
-        <v>16060846</v>
+        <v>8828315</v>
       </c>
       <c r="G11" s="1">
-        <v>0.022883106023073197</v>
+        <v>0.032769076526165009</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" t="s">
@@ -5456,22 +5429,22 @@
         <v>36138868</v>
       </c>
       <c r="B12" s="2">
-        <v>158931795.54154471</v>
+        <v>105620875.73033711</v>
       </c>
       <c r="C12" s="2">
-        <v>461327470428160</v>
+        <v>168397144850432</v>
       </c>
       <c r="D12" s="1">
-        <v>0.98006892204284668</v>
+        <v>0.98007315397262573</v>
       </c>
       <c r="E12" s="2">
-        <v>198024802.40849441</v>
+        <v>119968863.35415804</v>
       </c>
       <c r="F12" s="1">
-        <v>16060846</v>
+        <v>8828315</v>
       </c>
       <c r="G12" s="1">
-        <v>0.03436824306845665</v>
+        <v>0.056777879595756531</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" t="s">
@@ -5483,22 +5456,22 @@
         <v>36138868</v>
       </c>
       <c r="B13" s="2">
-        <v>256128225.94424459</v>
+        <v>139201032.40324032</v>
       </c>
       <c r="C13" s="2">
-        <v>724627890372608</v>
+        <v>216804613947392</v>
       </c>
       <c r="D13" s="1">
-        <v>0.99003440141677857</v>
+        <v>0.99003446102142334</v>
       </c>
       <c r="E13" s="2">
-        <v>264121386.09018332</v>
+        <v>140365105.10628724</v>
       </c>
       <c r="F13" s="1">
-        <v>16060846</v>
+        <v>8828315</v>
       </c>
       <c r="G13" s="1">
-        <v>0.038492675870656967</v>
+        <v>0.071873560547828674</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" t="s">
@@ -5510,22 +5483,22 @@
         <v>36138868</v>
       </c>
       <c r="B14" s="2">
-        <v>275122292.97929794</v>
+        <v>141758638.8576569</v>
       </c>
       <c r="C14" s="2">
-        <v>775097715523584</v>
+        <v>225180035055616</v>
       </c>
       <c r="D14" s="1">
-        <v>0.99101871252059937</v>
+        <v>0.99101853370666504</v>
       </c>
       <c r="E14" s="2">
-        <v>284595636.77256119</v>
+        <v>143762394.3729271</v>
       </c>
       <c r="F14" s="1">
-        <v>16060846</v>
+        <v>8828315</v>
       </c>
       <c r="G14" s="1">
-        <v>0.037923015654087067</v>
+        <v>0.075888410210609436</v>
       </c>
       <c r="H14" s="1"/>
       <c r="I14" t="s">
@@ -5537,22 +5510,22 @@
         <v>36138868</v>
       </c>
       <c r="B15" s="2">
-        <v>297594138.25714928</v>
+        <v>145787260.51743525</v>
       </c>
       <c r="C15" s="2">
-        <v>835467910053888</v>
+        <v>235203062661120</v>
       </c>
       <c r="D15" s="1">
-        <v>0.99200296401977539</v>
+        <v>0.99200302362442017</v>
       </c>
       <c r="E15" s="2">
-        <v>310708674.5301879</v>
+        <v>149640096.33887291</v>
       </c>
       <c r="F15" s="1">
-        <v>16060846</v>
+        <v>8828315</v>
       </c>
       <c r="G15" s="1">
-        <v>0.038010518997907639</v>
+        <v>0.078476198017597198</v>
       </c>
       <c r="H15" s="1"/>
       <c r="I15" t="s">
@@ -5564,22 +5537,22 @@
         <v>36138868</v>
       </c>
       <c r="B16" s="2">
-        <v>328526953.66621685</v>
+        <v>153246643.49977508</v>
       </c>
       <c r="C16" s="2">
-        <v>919804693184512</v>
+        <v>248953987661824</v>
       </c>
       <c r="D16" s="1">
         <v>0.9931102991104126</v>
       </c>
       <c r="E16" s="2">
-        <v>343443481.4575308</v>
+        <v>157311533.45704004</v>
       </c>
       <c r="F16" s="1">
-        <v>16060846</v>
+        <v>8828315</v>
       </c>
       <c r="G16" s="1">
-        <v>0.039304561913013458</v>
+        <v>0.086898952722549439</v>
       </c>
       <c r="H16" s="1"/>
       <c r="I16" t="s">
@@ -5591,22 +5564,22 @@
         <v>36138868</v>
       </c>
       <c r="B17" s="2">
-        <v>363905713.06498766</v>
+        <v>160272408.90688261</v>
       </c>
       <c r="C17" s="2">
-        <v>1015856804921344</v>
+        <v>264226941698048</v>
       </c>
       <c r="D17" s="1">
-        <v>0.99409443140029907</v>
+        <v>0.99409449100494385</v>
       </c>
       <c r="E17" s="2">
-        <v>382906053.01922864</v>
+        <v>164197460.55443093</v>
       </c>
       <c r="F17" s="1">
-        <v>16060846</v>
+        <v>8828315</v>
       </c>
       <c r="G17" s="1">
-        <v>0.03923579677939415</v>
+        <v>0.089875593781471253</v>
       </c>
       <c r="H17" s="1"/>
       <c r="I17" t="s">
@@ -5618,22 +5591,22 @@
         <v>36138868</v>
       </c>
       <c r="B18" s="2">
-        <v>409246147.77327937</v>
+        <v>170110008.08988762</v>
       </c>
       <c r="C18" s="2">
-        <v>1142455529373696</v>
+        <v>284231573962752</v>
       </c>
       <c r="D18" s="1">
-        <v>0.99507874250411987</v>
+        <v>0.9950786828994751</v>
       </c>
       <c r="E18" s="2">
-        <v>433964935.9010402</v>
+        <v>177186848.59303403</v>
       </c>
       <c r="F18" s="1">
-        <v>16060846</v>
+        <v>8828315</v>
       </c>
       <c r="G18" s="1">
-        <v>0.03933330625295639</v>
+        <v>0.095529280602931976</v>
       </c>
       <c r="H18" s="1"/>
       <c r="I18" t="s">
@@ -5645,22 +5618,22 @@
         <v>36138868</v>
       </c>
       <c r="B19" s="2">
-        <v>469988477.27272725</v>
+        <v>181805881.94288284</v>
       </c>
       <c r="C19" s="2">
-        <v>1319580651749376</v>
+        <v>310995427786752</v>
       </c>
       <c r="D19" s="1">
         <v>0.9960629940032959</v>
       </c>
       <c r="E19" s="2">
-        <v>503915180.83162308</v>
+        <v>195419124.56776586</v>
       </c>
       <c r="F19" s="1">
-        <v>16060846</v>
+        <v>8828315</v>
       </c>
       <c r="G19" s="1">
-        <v>0.038623616099357605</v>
+        <v>0.10042359679937363</v>
       </c>
       <c r="H19" s="1"/>
       <c r="I19" t="s">
@@ -5672,22 +5645,22 @@
         <v>36138868</v>
       </c>
       <c r="B20" s="2">
-        <v>561474737.12615252</v>
+        <v>215230481.88976374</v>
       </c>
       <c r="C20" s="2">
-        <v>1591464026963968</v>
+        <v>349522995707904</v>
       </c>
       <c r="D20" s="1">
-        <v>0.99704724550247192</v>
+        <v>0.9970473051071167</v>
       </c>
       <c r="E20" s="2">
-        <v>632094479.39274669</v>
+        <v>221738918.74718848</v>
       </c>
       <c r="F20" s="1">
-        <v>16060846</v>
+        <v>8828315</v>
       </c>
       <c r="G20" s="1">
-        <v>0.040356032550334931</v>
+        <v>0.11489391326904297</v>
       </c>
       <c r="H20" s="1"/>
       <c r="I20" t="s">
@@ -5699,22 +5672,22 @@
         <v>36138868</v>
       </c>
       <c r="B21" s="2">
-        <v>747043842.78002703</v>
+        <v>229270627.98020685</v>
       </c>
       <c r="C21" s="2">
-        <v>2071155502481408</v>
+        <v>413412379066368</v>
       </c>
       <c r="D21" s="1">
         <v>0.99803149700164795</v>
       </c>
       <c r="E21" s="2">
-        <v>907114024.40258658</v>
+        <v>257671550.60444197</v>
       </c>
       <c r="F21" s="1">
-        <v>16060846</v>
+        <v>8828315</v>
       </c>
       <c r="G21" s="1">
-        <v>0.03724316880106926</v>
+        <v>0.13033302128314972</v>
       </c>
       <c r="H21" s="1"/>
       <c r="I21" t="s">
@@ -5726,22 +5699,22 @@
         <v>36138868</v>
       </c>
       <c r="B22" s="2">
-        <v>1221202396.9860549</v>
+        <v>308270318.26360774</v>
       </c>
       <c r="C22" s="2">
-        <v>3235229749739520</v>
+        <v>569157590450176</v>
       </c>
       <c r="D22" s="1">
         <v>0.99901574850082397</v>
       </c>
       <c r="E22" s="2">
-        <v>1286490176.4507422</v>
+        <v>315192015.51956826</v>
       </c>
       <c r="F22" s="1">
-        <v>16060846</v>
+        <v>8828315</v>
       </c>
       <c r="G22" s="1">
-        <v>0.035288237035274506</v>
+        <v>0.1438007801771164</v>
       </c>
       <c r="H22" s="1"/>
       <c r="I22" t="s">
@@ -5753,22 +5726,22 @@
         <v>36138868</v>
       </c>
       <c r="B23" s="2">
-        <v>1518730880.1169591</v>
+        <v>336527213.22537118</v>
       </c>
       <c r="C23" s="2">
-        <v>3884785034330112</v>
+        <v>653809583915008</v>
       </c>
       <c r="D23" s="1">
         <v>0.99926179647445679</v>
       </c>
       <c r="E23" s="2">
-        <v>1630887642.9776227</v>
+        <v>348317631.39547962</v>
       </c>
       <c r="F23" s="1">
-        <v>16060846</v>
+        <v>8828315</v>
       </c>
       <c r="G23" s="1">
-        <v>0.030651843175292015</v>
+        <v>0.14318752288818359</v>
       </c>
       <c r="H23" s="1"/>
       <c r="I23" t="s">
@@ -5780,22 +5753,22 @@
         <v>36138868</v>
       </c>
       <c r="B24" s="2">
-        <v>2076127879.6671164</v>
+        <v>399186451.41700417</v>
       </c>
       <c r="C24" s="2">
-        <v>5011861225340928</v>
+        <v>806572712263680</v>
       </c>
       <c r="D24" s="1">
         <v>0.99950790405273438</v>
       </c>
       <c r="E24" s="2">
-        <v>2352320199.5051732</v>
+        <v>434471314.88978857</v>
       </c>
       <c r="F24" s="1">
-        <v>16060846</v>
+        <v>8828315</v>
       </c>
       <c r="G24" s="1">
-        <v>0.028645800426602364</v>
+        <v>0.15450634062290192</v>
       </c>
       <c r="H24" s="1"/>
       <c r="I24" t="s">
@@ -5807,22 +5780,22 @@
         <v>36138868</v>
       </c>
       <c r="B25" s="2">
-        <v>3769915217.9487181</v>
+        <v>595385494.82681036</v>
       </c>
       <c r="C25" s="2">
-        <v>7671401611788288</v>
+        <v>1178674183274496</v>
       </c>
       <c r="D25" s="1">
         <v>0.99975395202636719</v>
       </c>
       <c r="E25" s="2">
-        <v>7671401374.493928</v>
+        <v>1178674117.5213675</v>
       </c>
       <c r="F25" s="1">
-        <v>16060846</v>
+        <v>8828315</v>
       </c>
       <c r="G25" s="1">
-        <v>0.021463882178068161</v>
+        <v>0.13827565312385559</v>
       </c>
       <c r="H25" s="1"/>
       <c r="I25" t="s">
@@ -5872,22 +5845,22 @@
         <v>36806212</v>
       </c>
       <c r="B2" s="2">
-        <v>15938670.837867247</v>
+        <v>14814310.119695324</v>
       </c>
       <c r="C2" s="2">
-        <v>144072698232832</v>
+        <v>79722604134400</v>
       </c>
       <c r="D2" s="1">
         <v>0.86003190279006958</v>
       </c>
       <c r="E2" s="2">
-        <v>22789482.318390995</v>
+        <v>21194865.223321665</v>
       </c>
       <c r="F2" s="1">
-        <v>20232044</v>
+        <v>11220019</v>
       </c>
       <c r="G2" s="1">
-        <v>7.207115413621068e-05</v>
+        <v>7.7349301136564463e-05</v>
       </c>
       <c r="H2" s="1">
         <v>2022</v>
@@ -5901,22 +5874,22 @@
         <v>36806212</v>
       </c>
       <c r="B3" s="2">
-        <v>29025226.470052794</v>
+        <v>27006870.43224055</v>
       </c>
       <c r="C3" s="2">
-        <v>153423882223616</v>
+        <v>84235213864960</v>
       </c>
       <c r="D3" s="1">
         <v>0.87005120515823364</v>
       </c>
       <c r="E3" s="2">
-        <v>33994713.429565489</v>
+        <v>31429705.973772354</v>
       </c>
       <c r="F3" s="1">
-        <v>20232044</v>
+        <v>11220019</v>
       </c>
       <c r="G3" s="1">
-        <v>5.8275232731830329e-05</v>
+        <v>8.9641005615703762e-05</v>
       </c>
       <c r="H3" s="1"/>
       <c r="I3" t="s">
@@ -5928,22 +5901,22 @@
         <v>36806212</v>
       </c>
       <c r="B4" s="2">
-        <v>38794828.913912095</v>
+        <v>35520744.164843172</v>
       </c>
       <c r="C4" s="2">
-        <v>163401057697792</v>
+        <v>88645751013376</v>
       </c>
       <c r="D4" s="1">
-        <v>0.88007020950317383</v>
+        <v>0.88006842136383057</v>
       </c>
       <c r="E4" s="2">
-        <v>42442013.412226677</v>
+        <v>39102647.82757885</v>
       </c>
       <c r="F4" s="1">
-        <v>20232044</v>
+        <v>11220019</v>
       </c>
       <c r="G4" s="1">
-        <v>0.00037697658990509808</v>
+        <v>0.00041426648385822773</v>
       </c>
       <c r="H4" s="1"/>
       <c r="I4" t="s">
@@ -5955,22 +5928,22 @@
         <v>36806212</v>
       </c>
       <c r="B5" s="2">
-        <v>46185617.211766854</v>
+        <v>41860866.39970877</v>
       </c>
       <c r="C5" s="2">
-        <v>174427379597312</v>
+        <v>93179944632320</v>
       </c>
       <c r="D5" s="1">
-        <v>0.89008939266204834</v>
+        <v>0.89012420177459717</v>
       </c>
       <c r="E5" s="2">
-        <v>49940447.945736751</v>
+        <v>44860357.983524017</v>
       </c>
       <c r="F5" s="1">
-        <v>20232044</v>
+        <v>11220019</v>
       </c>
       <c r="G5" s="1">
-        <v>0.0010147312423214316</v>
+        <v>0.0011439332738518715</v>
       </c>
       <c r="H5" s="1"/>
       <c r="I5" t="s">
@@ -5982,22 +5955,22 @@
         <v>36806212</v>
       </c>
       <c r="B6" s="2">
-        <v>53605276.588021778</v>
+        <v>47171686.880244091</v>
       </c>
       <c r="C6" s="2">
-        <v>186911742230528</v>
+        <v>97986164031488</v>
       </c>
       <c r="D6" s="1">
-        <v>0.90010726451873779</v>
+        <v>0.90006458759307861</v>
       </c>
       <c r="E6" s="2">
-        <v>56554070.756891333</v>
+        <v>49462305.578377605</v>
       </c>
       <c r="F6" s="1">
-        <v>20232044</v>
+        <v>11220019</v>
       </c>
       <c r="G6" s="1">
-        <v>0.0011960177216678858</v>
+        <v>0.0013759370194748044</v>
       </c>
       <c r="H6" s="1"/>
       <c r="I6" t="s">
@@ -6009,22 +5982,22 @@
         <v>36806212</v>
       </c>
       <c r="B7" s="2">
-        <v>59778395.043731779</v>
+        <v>52036938.942395046</v>
       </c>
       <c r="C7" s="2">
-        <v>201445441798144</v>
+        <v>103353891684352</v>
       </c>
       <c r="D7" s="1">
-        <v>0.91012728214263916</v>
+        <v>0.91001832485198975</v>
       </c>
       <c r="E7" s="2">
-        <v>63087842.181482867</v>
+        <v>53995999.525590971</v>
       </c>
       <c r="F7" s="1">
-        <v>20232044</v>
+        <v>11220019</v>
       </c>
       <c r="G7" s="1">
-        <v>0.0019257473759353161</v>
+        <v>0.0023033355828374624</v>
       </c>
       <c r="H7" s="1"/>
       <c r="I7" t="s">
@@ -6036,22 +6009,22 @@
         <v>36806212</v>
       </c>
       <c r="B8" s="2">
-        <v>66712280.825638242</v>
+        <v>56387090.244793572</v>
       </c>
       <c r="C8" s="2">
-        <v>218803602456576</v>
+        <v>109540473307136</v>
       </c>
       <c r="D8" s="1">
-        <v>0.92014569044113159</v>
+        <v>0.9200405478477478</v>
       </c>
       <c r="E8" s="2">
-        <v>70556034.397892341</v>
+        <v>58580488.98125273</v>
       </c>
       <c r="F8" s="1">
-        <v>20232044</v>
+        <v>11220019</v>
       </c>
       <c r="G8" s="1">
-        <v>0.0032909484580159187</v>
+        <v>0.0039406376890838146</v>
       </c>
       <c r="H8" s="1"/>
       <c r="I8" t="s">
@@ -6063,22 +6036,22 @@
         <v>36806212</v>
       </c>
       <c r="B9" s="2">
-        <v>74770623.89300561</v>
+        <v>60863232.334241599</v>
       </c>
       <c r="C9" s="2">
-        <v>239709322215424</v>
+        <v>116803992813568</v>
       </c>
       <c r="D9" s="1">
-        <v>0.93001490831375122</v>
+        <v>0.9300156831741333</v>
       </c>
       <c r="E9" s="2">
-        <v>79371219.12723288</v>
+        <v>63933597.260184824</v>
       </c>
       <c r="F9" s="1">
-        <v>20232044</v>
+        <v>11220019</v>
       </c>
       <c r="G9" s="1">
-        <v>0.0062387916259467602</v>
+        <v>0.0079050390049815178</v>
       </c>
       <c r="H9" s="1"/>
       <c r="I9" t="s">
@@ -6090,22 +6063,22 @@
         <v>36806212</v>
       </c>
       <c r="B10" s="2">
-        <v>84520731.437015146</v>
+        <v>66332378.117604211</v>
       </c>
       <c r="C10" s="2">
-        <v>266501865078784</v>
+        <v>125638212059136</v>
       </c>
       <c r="D10" s="1">
-        <v>0.94003504514694214</v>
+        <v>0.94003528356552124</v>
       </c>
       <c r="E10" s="2">
-        <v>90328209.885448992</v>
+        <v>69402681.370158449</v>
       </c>
       <c r="F10" s="1">
-        <v>20232044</v>
+        <v>11220019</v>
       </c>
       <c r="G10" s="1">
-        <v>0.010250932537019253</v>
+        <v>0.013299405574798584</v>
       </c>
       <c r="H10" s="1"/>
       <c r="I10" t="s">
@@ -6117,22 +6090,22 @@
         <v>36806212</v>
       </c>
       <c r="B11" s="2">
-        <v>97023860.940325499</v>
+        <v>72154106.074342698</v>
       </c>
       <c r="C11" s="2">
-        <v>301839765471232</v>
+        <v>136931232972800</v>
       </c>
       <c r="D11" s="1">
-        <v>0.95005357265472412</v>
+        <v>0.95006340742111206</v>
       </c>
       <c r="E11" s="2">
-        <v>105030296.43318109</v>
+        <v>77057941.180293739</v>
       </c>
       <c r="F11" s="1">
-        <v>20232044</v>
+        <v>11220019</v>
       </c>
       <c r="G11" s="1">
-        <v>0.014463942497968674</v>
+        <v>0.020183200016617775</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" t="s">
@@ -6144,22 +6117,22 @@
         <v>36806212</v>
       </c>
       <c r="B12" s="2">
-        <v>114361793.81818181</v>
+        <v>81557810.147299498</v>
       </c>
       <c r="C12" s="2">
-        <v>351229708337152</v>
+        <v>151984581640192</v>
       </c>
       <c r="D12" s="1">
-        <v>0.96007329225540161</v>
+        <v>0.96009606122970581</v>
       </c>
       <c r="E12" s="2">
-        <v>124877417.69285633</v>
+        <v>86035861.113073751</v>
       </c>
       <c r="F12" s="1">
-        <v>20232044</v>
+        <v>11220019</v>
       </c>
       <c r="G12" s="1">
-        <v>0.017344845458865166</v>
+        <v>0.024707911536097527</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" t="s">
@@ -6171,22 +6144,22 @@
         <v>36806212</v>
       </c>
       <c r="B13" s="2">
-        <v>137261080.03629765</v>
+        <v>93824706.68361789</v>
       </c>
       <c r="C13" s="2">
-        <v>427056483532800</v>
+        <v>174032343269376</v>
       </c>
       <c r="D13" s="1">
-        <v>0.97009223699569702</v>
+        <v>0.97009408473968506</v>
       </c>
       <c r="E13" s="2">
-        <v>157130937.93658885</v>
+        <v>104417424.76030323</v>
       </c>
       <c r="F13" s="1">
-        <v>20232044</v>
+        <v>11220019</v>
       </c>
       <c r="G13" s="1">
-        <v>0.025833776220679283</v>
+        <v>0.038908328860998154</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" t="s">
@@ -6198,22 +6171,22 @@
         <v>36806212</v>
       </c>
       <c r="B14" s="2">
-        <v>182942397.81818181</v>
+        <v>115867721.78811559</v>
       </c>
       <c r="C14" s="2">
-        <v>563035651440640</v>
+        <v>209094728220672</v>
       </c>
       <c r="D14" s="1">
-        <v>0.98011142015457153</v>
+        <v>0.98011130094528198</v>
       </c>
       <c r="E14" s="2">
-        <v>228137398.60832018</v>
+        <v>133187844.30361556</v>
       </c>
       <c r="F14" s="1">
-        <v>20232044</v>
+        <v>11220019</v>
       </c>
       <c r="G14" s="1">
-        <v>0.036253690719604492</v>
+        <v>0.062026955187320709</v>
       </c>
       <c r="H14" s="1"/>
       <c r="I14" t="s">
@@ -6225,22 +6198,22 @@
         <v>36806212</v>
       </c>
       <c r="B15" s="2">
-        <v>296777642.62354654</v>
+        <v>152596714.93459302</v>
       </c>
       <c r="C15" s="2">
-        <v>903007277416448</v>
+        <v>286153034956800</v>
       </c>
       <c r="D15" s="1">
         <v>0.9901304841041565</v>
       </c>
       <c r="E15" s="2">
-        <v>304773427.10068136</v>
+        <v>154597686.30954182</v>
       </c>
       <c r="F15" s="1">
-        <v>20232044</v>
+        <v>11220019</v>
       </c>
       <c r="G15" s="1">
-        <v>0.038716547191143036</v>
+        <v>0.076271183788776398</v>
       </c>
       <c r="H15" s="1"/>
       <c r="I15" t="s">
@@ -6252,22 +6225,22 @@
         <v>36806212</v>
       </c>
       <c r="B16" s="2">
-        <v>316848909.14046884</v>
+        <v>156530524.16424415</v>
       </c>
       <c r="C16" s="2">
-        <v>962833420386304</v>
+        <v>299308318457856</v>
       </c>
       <c r="D16" s="1">
         <v>0.99102771282196045</v>
       </c>
       <c r="E16" s="2">
-        <v>328438399.8338784</v>
+        <v>160159555.20660299</v>
       </c>
       <c r="F16" s="1">
-        <v>20232044</v>
+        <v>11220019</v>
       </c>
       <c r="G16" s="1">
-        <v>0.039233576506376267</v>
+        <v>0.081427685916423798</v>
       </c>
       <c r="H16" s="1"/>
       <c r="I16" t="s">
@@ -6279,22 +6252,22 @@
         <v>36806212</v>
       </c>
       <c r="B17" s="2">
-        <v>344992363.19040698</v>
+        <v>164125317.9505814</v>
       </c>
       <c r="C17" s="2">
-        <v>1046617897566208</v>
+        <v>317686684844032</v>
       </c>
       <c r="D17" s="1">
         <v>0.99207448959350586</v>
       </c>
       <c r="E17" s="2">
-        <v>359057448.51929718</v>
+        <v>166723476.43150082</v>
       </c>
       <c r="F17" s="1">
-        <v>20232044</v>
+        <v>11220019</v>
       </c>
       <c r="G17" s="1">
-        <v>0.039439283311367035</v>
+        <v>0.084439121186733246</v>
       </c>
       <c r="H17" s="1"/>
       <c r="I17" t="s">
@@ -6306,22 +6279,22 @@
         <v>36806212</v>
       </c>
       <c r="B18" s="2">
-        <v>379433123.54651165</v>
+        <v>168604224.70481378</v>
       </c>
       <c r="C18" s="2">
-        <v>1151251085524992</v>
+        <v>340658384535552</v>
       </c>
       <c r="D18" s="1">
-        <v>0.99312126636505127</v>
+        <v>0.9931212067604065</v>
       </c>
       <c r="E18" s="2">
-        <v>393896079.76258969</v>
+        <v>170881205.99545798</v>
       </c>
       <c r="F18" s="1">
-        <v>20232044</v>
+        <v>11220019</v>
       </c>
       <c r="G18" s="1">
-        <v>0.038916315883398056</v>
+        <v>0.088536277413368225</v>
       </c>
       <c r="H18" s="1"/>
       <c r="I18" t="s">
@@ -6333,22 +6306,22 @@
         <v>36806212</v>
       </c>
       <c r="B19" s="2">
-        <v>415870981.2863372</v>
+        <v>174708133.95129049</v>
       </c>
       <c r="C19" s="2">
-        <v>1264852299415552</v>
+        <v>366126064205824</v>
       </c>
       <c r="D19" s="1">
         <v>0.99401849508285522</v>
       </c>
       <c r="E19" s="2">
-        <v>438170736.23692483</v>
+        <v>179691358.11985779</v>
       </c>
       <c r="F19" s="1">
-        <v>20232044</v>
+        <v>11220019</v>
       </c>
       <c r="G19" s="1">
-        <v>0.038815770298242569</v>
+        <v>0.091620862483978271</v>
       </c>
       <c r="H19" s="1"/>
       <c r="I19" t="s">
@@ -6360,22 +6333,22 @@
         <v>36806212</v>
       </c>
       <c r="B20" s="2">
-        <v>470377274.39578414</v>
+        <v>191949423.58713436</v>
       </c>
       <c r="C20" s="2">
-        <v>1440206418870272</v>
+        <v>405674693492736</v>
       </c>
       <c r="D20" s="1">
-        <v>0.99506521224975586</v>
+        <v>0.99506527185440064</v>
       </c>
       <c r="E20" s="2">
-        <v>497726667.20307314</v>
+        <v>201246837.38254687</v>
       </c>
       <c r="F20" s="1">
-        <v>20232044</v>
+        <v>11220019</v>
       </c>
       <c r="G20" s="1">
-        <v>0.037553787231445313</v>
+        <v>0.095935538411140442</v>
       </c>
       <c r="H20" s="1"/>
       <c r="I20" t="s">
@@ -6387,22 +6360,22 @@
         <v>36806212</v>
       </c>
       <c r="B21" s="2">
-        <v>545496419.69476748</v>
+        <v>226764225.65406978</v>
       </c>
       <c r="C21" s="2">
-        <v>1693954697330688</v>
+        <v>460710874185728</v>
       </c>
       <c r="D21" s="1">
         <v>0.99611198902130127</v>
       </c>
       <c r="E21" s="2">
-        <v>589767016.17005825</v>
+        <v>233066171.42078492</v>
       </c>
       <c r="F21" s="1">
-        <v>20232044</v>
+        <v>11220019</v>
       </c>
       <c r="G21" s="1">
-        <v>0.042729936540126801</v>
+        <v>0.10814506560564041</v>
       </c>
       <c r="H21" s="1"/>
       <c r="I21" t="s">
@@ -6414,22 +6387,22 @@
         <v>36806212</v>
       </c>
       <c r="B22" s="2">
-        <v>661942009.99273253</v>
+        <v>243908688.40843022</v>
       </c>
       <c r="C22" s="2">
-        <v>2025216934936576</v>
+        <v>529005551812608</v>
       </c>
       <c r="D22" s="1">
         <v>0.99700927734375</v>
       </c>
       <c r="E22" s="2">
-        <v>754407222.1558907</v>
+        <v>257693380.1749422</v>
       </c>
       <c r="F22" s="1">
-        <v>20232044</v>
+        <v>11220019</v>
       </c>
       <c r="G22" s="1">
-        <v>0.04088427871465683</v>
+        <v>0.11928960680961609</v>
       </c>
       <c r="H22" s="1"/>
       <c r="I22" t="s">
@@ -6441,22 +6414,22 @@
         <v>36806212</v>
       </c>
       <c r="B23" s="2">
-        <v>913295823.2194767</v>
+        <v>286138052.32558137</v>
       </c>
       <c r="C23" s="2">
-        <v>2709490856099840</v>
+        <v>675094904963072</v>
       </c>
       <c r="D23" s="1">
         <v>0.99805599451065063</v>
       </c>
       <c r="E23" s="2">
-        <v>1146484477.6785715</v>
+        <v>330683532.67753327</v>
       </c>
       <c r="F23" s="1">
-        <v>20232044</v>
+        <v>11220019</v>
       </c>
       <c r="G23" s="1">
-        <v>0.037903748452663422</v>
+        <v>0.13050152361392975</v>
       </c>
       <c r="H23" s="1"/>
       <c r="I23" t="s">
@@ -6468,22 +6441,22 @@
         <v>36806212</v>
       </c>
       <c r="B24" s="2">
-        <v>1653761198.5828488</v>
+        <v>427286992.36918604</v>
       </c>
       <c r="C24" s="2">
-        <v>4533053439344640</v>
+        <v>1076920435343360</v>
       </c>
       <c r="D24" s="1">
         <v>0.99910277128219605</v>
       </c>
       <c r="E24" s="2">
-        <v>1785917779.2514536</v>
+        <v>447634851.10828489</v>
       </c>
       <c r="F24" s="1">
-        <v>20232044</v>
+        <v>11220019</v>
       </c>
       <c r="G24" s="1">
-        <v>0.033393625169992447</v>
+        <v>0.13295415043830872</v>
       </c>
       <c r="H24" s="1"/>
       <c r="I24" t="s">
@@ -6495,22 +6468,22 @@
         <v>36806212</v>
       </c>
       <c r="B25" s="2">
-        <v>2304009746.729651</v>
+        <v>538345856.64970911</v>
       </c>
       <c r="C25" s="2">
-        <v>5906683838595072</v>
+        <v>1391577456967680</v>
       </c>
       <c r="D25" s="1">
         <v>0.99940186738967896</v>
       </c>
       <c r="E25" s="2">
-        <v>2619027571.6751447</v>
+        <v>590410406.06831396</v>
       </c>
       <c r="F25" s="1">
-        <v>20232044</v>
+        <v>11220019</v>
       </c>
       <c r="G25" s="1">
-        <v>0.03071993961930275</v>
+        <v>0.13566496968269348</v>
       </c>
       <c r="H25" s="1"/>
       <c r="I25" t="s">
@@ -6522,22 +6495,22 @@
         <v>36806212</v>
       </c>
       <c r="B26" s="2">
-        <v>4210367716.5697675</v>
+        <v>890491295.05813956</v>
       </c>
       <c r="C26" s="2">
-        <v>9194639143731200</v>
+        <v>2192817430462464</v>
       </c>
       <c r="D26" s="1">
         <v>0.99970096349716187</v>
       </c>
       <c r="E26" s="2">
-        <v>9194639213.863903</v>
+        <v>2192817352.9572091</v>
       </c>
       <c r="F26" s="1">
-        <v>20232044</v>
+        <v>11220019</v>
       </c>
       <c r="G26" s="1">
-        <v>0.024515798315405846</v>
+        <v>0.10874081403017044</v>
       </c>
       <c r="H26" s="1"/>
       <c r="I26" t="s">
